--- a/res/fonts/sortingOrder.xlsx
+++ b/res/fonts/sortingOrder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\msys64\c47\c43\res\fonts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500AA545-EF60-43E7-915C-DEB8E08178E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B0FFDE-D48E-40E8-973A-65B13713A357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13656" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="2075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="2076">
   <si>
     <t>Code point</t>
   </si>
@@ -6321,9 +6321,6 @@
     <t>HP period</t>
   </si>
   <si>
-    <t>U+0459</t>
-  </si>
-  <si>
     <t>U+25B6</t>
   </si>
   <si>
@@ -6361,6 +6358,12 @@
   </si>
   <si>
     <t>BLACK SMALL SQUARE</t>
+  </si>
+  <si>
+    <t>U+2404</t>
+  </si>
+  <si>
+    <t>SYMBOL FOR END OF TRANSMISSION</t>
   </si>
 </sst>
 </file>
@@ -18572,127 +18575,127 @@
     </row>
     <row r="358" spans="1:9" ht="16.95" customHeight="1">
       <c r="A358" s="1" t="s">
-        <v>2061</v>
+        <v>1036</v>
       </c>
       <c r="B358" s="5">
         <f>IF(ISNA(VLOOKUP(H358,$A$2:$C$1028,3,1)),C358,VLOOKUP(H358,$A$2:$C$1028,3,1))</f>
-        <v>569</v>
+        <v>319</v>
       </c>
       <c r="C358" s="1">
-        <v>570</v>
+        <v>323</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>303</v>
+        <v>1037</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>1538</v>
+        <v>1038</v>
       </c>
       <c r="F358" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A358,3,4)))</f>
-        <v>љ</v>
+        <v>ᵀ</v>
       </c>
       <c r="G358" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A358,3,4)))</f>
-        <v>љ</v>
+        <v>ᵀ</v>
       </c>
       <c r="H358" s="1" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I358" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H358,3,4)))</f>
-        <v>_</v>
+        <v>T</v>
       </c>
     </row>
     <row r="359" spans="1:9" ht="16.95" customHeight="1">
       <c r="A359" s="1" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B359" s="5">
         <f>IF(ISNA(VLOOKUP(H359,$A$2:$C$1028,3,1)),C359,VLOOKUP(H359,$A$2:$C$1028,3,1))</f>
-        <v>319</v>
+        <v>162</v>
       </c>
       <c r="C359" s="1">
-        <v>323</v>
+        <v>166</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="F359" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A359,3,4)))</f>
-        <v>ᵀ</v>
+        <v>ᵍ</v>
       </c>
       <c r="G359" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A359,3,4)))</f>
-        <v>ᵀ</v>
+        <v>ᵍ</v>
       </c>
       <c r="H359" s="1" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="I359" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H359,3,4)))</f>
-        <v>T</v>
+        <v>G</v>
       </c>
     </row>
     <row r="360" spans="1:9" ht="16.95" customHeight="1">
       <c r="A360" s="1" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="B360" s="5">
         <f>IF(ISNA(VLOOKUP(H360,$A$2:$C$1028,3,1)),C360,VLOOKUP(H360,$A$2:$C$1028,3,1))</f>
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C360" s="1">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="F360" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A360,3,4)))</f>
-        <v>ᵍ</v>
+        <v>ᶠ</v>
       </c>
       <c r="G360" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A360,3,4)))</f>
-        <v>ᵍ</v>
+        <v>ᶠ</v>
       </c>
       <c r="H360" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I360" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H360,3,4)))</f>
-        <v>G</v>
+        <v>F</v>
       </c>
     </row>
     <row r="361" spans="1:9" ht="16.95" customHeight="1">
       <c r="A361" s="1" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B361" s="5">
         <f>IF(ISNA(VLOOKUP(H361,$A$2:$C$1028,3,1)),C361,VLOOKUP(H361,$A$2:$C$1028,3,1))</f>
         <v>153</v>
       </c>
       <c r="C361" s="1">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="F361" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A361,3,4)))</f>
-        <v>ᶠ</v>
+        <v>ẝ</v>
       </c>
       <c r="G361" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A361,3,4)))</f>
-        <v>ᶠ</v>
+        <v>ẝ</v>
       </c>
       <c r="H361" s="1" t="s">
         <v>135</v>
@@ -18704,94 +18707,94 @@
     </row>
     <row r="362" spans="1:9" ht="16.95" customHeight="1">
       <c r="A362" s="1" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B362" s="5">
         <f>IF(ISNA(VLOOKUP(H362,$A$2:$C$1028,3,1)),C362,VLOOKUP(H362,$A$2:$C$1028,3,1))</f>
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C362" s="1">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>1046</v>
+        <v>849</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="F362" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A362,3,4)))</f>
-        <v>ẝ</v>
+        <v>ẟ</v>
       </c>
       <c r="G362" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A362,3,4)))</f>
-        <v>ẝ</v>
+        <v>ẟ</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I362" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H362,3,4)))</f>
-        <v>F</v>
+        <v>G</v>
       </c>
     </row>
     <row r="363" spans="1:9" ht="16.95" customHeight="1">
       <c r="A363" s="1" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B363" s="5">
         <f>IF(ISNA(VLOOKUP(H363,$A$2:$C$1028,3,1)),C363,VLOOKUP(H363,$A$2:$C$1028,3,1))</f>
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="C363" s="1">
-        <v>171</v>
+        <v>2</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>849</v>
+        <v>1051</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="F363" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A363,3,4)))</f>
-        <v>ẟ</v>
+        <v> </v>
       </c>
       <c r="G363" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A363,3,4)))</f>
-        <v>ẟ</v>
+        <v> </v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>138</v>
+        <v>9</v>
       </c>
       <c r="I363" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H363,3,4)))</f>
-        <v>G</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="364" spans="1:9" ht="16.95" customHeight="1">
       <c r="A364" s="1" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B364" s="5">
         <f>IF(ISNA(VLOOKUP(H364,$A$2:$C$1028,3,1)),C364,VLOOKUP(H364,$A$2:$C$1028,3,1))</f>
         <v>1</v>
       </c>
       <c r="C364" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="F364" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A364,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="G364" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A364,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="H364" s="1" t="s">
         <v>9</v>
@@ -18803,28 +18806,28 @@
     </row>
     <row r="365" spans="1:9" ht="16.95" customHeight="1">
       <c r="A365" s="1" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B365" s="5">
         <f>IF(ISNA(VLOOKUP(H365,$A$2:$C$1028,3,1)),C365,VLOOKUP(H365,$A$2:$C$1028,3,1))</f>
         <v>1</v>
       </c>
       <c r="C365" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="F365" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A365,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="G365" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A365,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="H365" s="1" t="s">
         <v>9</v>
@@ -18836,28 +18839,28 @@
     </row>
     <row r="366" spans="1:9" ht="16.95" customHeight="1">
       <c r="A366" s="1" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B366" s="5">
         <f>IF(ISNA(VLOOKUP(H366,$A$2:$C$1028,3,1)),C366,VLOOKUP(H366,$A$2:$C$1028,3,1))</f>
         <v>1</v>
       </c>
       <c r="C366" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="F366" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A366,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="G366" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A366,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="H366" s="1" t="s">
         <v>9</v>
@@ -18869,28 +18872,28 @@
     </row>
     <row r="367" spans="1:9" ht="16.95" customHeight="1">
       <c r="A367" s="1" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="B367" s="5">
         <f>IF(ISNA(VLOOKUP(H367,$A$2:$C$1028,3,1)),C367,VLOOKUP(H367,$A$2:$C$1028,3,1))</f>
         <v>1</v>
       </c>
       <c r="C367" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="F367" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A367,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="G367" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A367,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="H367" s="1" t="s">
         <v>9</v>
@@ -18902,28 +18905,28 @@
     </row>
     <row r="368" spans="1:9" ht="16.95" customHeight="1">
       <c r="A368" s="1" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B368" s="5">
         <f>IF(ISNA(VLOOKUP(H368,$A$2:$C$1028,3,1)),C368,VLOOKUP(H368,$A$2:$C$1028,3,1))</f>
         <v>1</v>
       </c>
       <c r="C368" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="F368" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A368,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="G368" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A368,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="H368" s="1" t="s">
         <v>9</v>
@@ -18935,28 +18938,28 @@
     </row>
     <row r="369" spans="1:9" ht="16.95" customHeight="1">
       <c r="A369" s="1" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B369" s="5">
         <f>IF(ISNA(VLOOKUP(H369,$A$2:$C$1028,3,1)),C369,VLOOKUP(H369,$A$2:$C$1028,3,1))</f>
         <v>1</v>
       </c>
       <c r="C369" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="F369" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A369,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="G369" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A369,3,4)))</f>
-        <v> </v>
+        <v> </v>
       </c>
       <c r="H369" s="1" t="s">
         <v>9</v>
@@ -18968,61 +18971,61 @@
     </row>
     <row r="370" spans="1:9" ht="16.95" customHeight="1">
       <c r="A370" s="1" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B370" s="5">
         <f>IF(ISNA(VLOOKUP(H370,$A$2:$C$1028,3,1)),C370,VLOOKUP(H370,$A$2:$C$1028,3,1))</f>
-        <v>1</v>
+        <v>555</v>
       </c>
       <c r="C370" s="1">
-        <v>8</v>
+        <v>556</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="F370" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A370,3,4)))</f>
-        <v> </v>
+        <v>‘</v>
       </c>
       <c r="G370" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A370,3,4)))</f>
-        <v> </v>
+        <v>‘</v>
       </c>
       <c r="H370" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I370" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H370,3,4)))</f>
-        <v xml:space="preserve"> </v>
+        <v>'</v>
       </c>
     </row>
     <row r="371" spans="1:9" ht="16.95" customHeight="1">
       <c r="A371" s="1" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B371" s="5">
         <f>IF(ISNA(VLOOKUP(H371,$A$2:$C$1028,3,1)),C371,VLOOKUP(H371,$A$2:$C$1028,3,1))</f>
         <v>555</v>
       </c>
       <c r="C371" s="1">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F371" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A371,3,4)))</f>
-        <v>‘</v>
+        <v>’</v>
       </c>
       <c r="G371" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A371,3,4)))</f>
-        <v>‘</v>
+        <v>’</v>
       </c>
       <c r="H371" s="1" t="s">
         <v>32</v>
@@ -19034,28 +19037,28 @@
     </row>
     <row r="372" spans="1:9" ht="16.95" customHeight="1">
       <c r="A372" s="1" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B372" s="5">
         <f>IF(ISNA(VLOOKUP(H372,$A$2:$C$1028,3,1)),C372,VLOOKUP(H372,$A$2:$C$1028,3,1))</f>
         <v>555</v>
       </c>
       <c r="C372" s="1">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="F372" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A372,3,4)))</f>
-        <v>’</v>
+        <v>‚</v>
       </c>
       <c r="G372" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A372,3,4)))</f>
-        <v>’</v>
+        <v>‚</v>
       </c>
       <c r="H372" s="1" t="s">
         <v>32</v>
@@ -19067,28 +19070,28 @@
     </row>
     <row r="373" spans="1:9" ht="16.95" customHeight="1">
       <c r="A373" s="1" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B373" s="5">
         <f>IF(ISNA(VLOOKUP(H373,$A$2:$C$1028,3,1)),C373,VLOOKUP(H373,$A$2:$C$1028,3,1))</f>
         <v>555</v>
       </c>
       <c r="C373" s="1">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="F373" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A373,3,4)))</f>
-        <v>‚</v>
+        <v>‛</v>
       </c>
       <c r="G373" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A373,3,4)))</f>
-        <v>‚</v>
+        <v>‛</v>
       </c>
       <c r="H373" s="1" t="s">
         <v>32</v>
@@ -19100,61 +19103,61 @@
     </row>
     <row r="374" spans="1:9" ht="16.95" customHeight="1">
       <c r="A374" s="1" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="B374" s="5">
         <f>IF(ISNA(VLOOKUP(H374,$A$2:$C$1028,3,1)),C374,VLOOKUP(H374,$A$2:$C$1028,3,1))</f>
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C374" s="1">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="F374" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A374,3,4)))</f>
-        <v>‛</v>
+        <v>“</v>
       </c>
       <c r="G374" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A374,3,4)))</f>
-        <v>‛</v>
+        <v>“</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I374" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H374,3,4)))</f>
-        <v>'</v>
+        <v>"</v>
       </c>
     </row>
     <row r="375" spans="1:9" ht="16.95" customHeight="1">
       <c r="A375" s="1" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="B375" s="5">
         <f>IF(ISNA(VLOOKUP(H375,$A$2:$C$1028,3,1)),C375,VLOOKUP(H375,$A$2:$C$1028,3,1))</f>
         <v>561</v>
       </c>
       <c r="C375" s="1">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="F375" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A375,3,4)))</f>
-        <v>“</v>
+        <v>”</v>
       </c>
       <c r="G375" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A375,3,4)))</f>
-        <v>“</v>
+        <v>”</v>
       </c>
       <c r="H375" s="1" t="s">
         <v>15</v>
@@ -19166,28 +19169,28 @@
     </row>
     <row r="376" spans="1:9" ht="16.95" customHeight="1">
       <c r="A376" s="1" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B376" s="5">
         <f>IF(ISNA(VLOOKUP(H376,$A$2:$C$1028,3,1)),C376,VLOOKUP(H376,$A$2:$C$1028,3,1))</f>
         <v>561</v>
       </c>
       <c r="C376" s="1">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F376" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A376,3,4)))</f>
-        <v>”</v>
+        <v>„</v>
       </c>
       <c r="G376" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A376,3,4)))</f>
-        <v>”</v>
+        <v>„</v>
       </c>
       <c r="H376" s="1" t="s">
         <v>15</v>
@@ -19199,28 +19202,28 @@
     </row>
     <row r="377" spans="1:9" ht="16.95" customHeight="1">
       <c r="A377" s="1" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B377" s="5">
         <f>IF(ISNA(VLOOKUP(H377,$A$2:$C$1028,3,1)),C377,VLOOKUP(H377,$A$2:$C$1028,3,1))</f>
         <v>561</v>
       </c>
       <c r="C377" s="1">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="F377" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A377,3,4)))</f>
-        <v>„</v>
+        <v>‟</v>
       </c>
       <c r="G377" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A377,3,4)))</f>
-        <v>„</v>
+        <v>‟</v>
       </c>
       <c r="H377" s="1" t="s">
         <v>15</v>
@@ -19231,62 +19234,62 @@
       </c>
     </row>
     <row r="378" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A378" s="1" t="s">
-        <v>1092</v>
+      <c r="A378" s="22" t="s">
+        <v>2058</v>
       </c>
       <c r="B378" s="5">
         <f>IF(ISNA(VLOOKUP(H378,$A$2:$C$1028,3,1)),C378,VLOOKUP(H378,$A$2:$C$1028,3,1))</f>
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="C378" s="1">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>1093</v>
+        <v>2059</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>1094</v>
+        <v>2060</v>
       </c>
       <c r="F378" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A378,3,4)))</f>
-        <v>‟</v>
+        <v>․</v>
       </c>
       <c r="G378" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A378,3,4)))</f>
-        <v>‟</v>
+        <v>․</v>
       </c>
       <c r="H378" s="1" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="I378" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H378,3,4)))</f>
-        <v>"</v>
+        <v>.</v>
       </c>
     </row>
     <row r="379" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A379" s="22" t="s">
-        <v>2058</v>
+      <c r="A379" s="1" t="s">
+        <v>1095</v>
       </c>
       <c r="B379" s="5">
         <f>IF(ISNA(VLOOKUP(H379,$A$2:$C$1028,3,1)),C379,VLOOKUP(H379,$A$2:$C$1028,3,1))</f>
         <v>541</v>
       </c>
       <c r="C379" s="1">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>2059</v>
+        <v>1096</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>2060</v>
+        <v>1097</v>
       </c>
       <c r="F379" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A379,3,4)))</f>
-        <v>․</v>
+        <v>…</v>
       </c>
       <c r="G379" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A379,3,4)))</f>
-        <v>․</v>
+        <v>…</v>
       </c>
       <c r="H379" s="1" t="s">
         <v>59</v>
@@ -19298,556 +19301,556 @@
     </row>
     <row r="380" spans="1:9" ht="16.95" customHeight="1">
       <c r="A380" s="1" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="B380" s="5">
         <f>IF(ISNA(VLOOKUP(H380,$A$2:$C$1028,3,1)),C380,VLOOKUP(H380,$A$2:$C$1028,3,1))</f>
-        <v>541</v>
+        <v>18</v>
       </c>
       <c r="C380" s="1">
-        <v>543</v>
+        <v>19</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F380" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A380,3,4)))</f>
-        <v>…</v>
+        <v>‧</v>
       </c>
       <c r="G380" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A380,3,4)))</f>
-        <v>…</v>
+        <v>‧</v>
       </c>
       <c r="H380" s="1" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="I380" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H380,3,4)))</f>
-        <v>.</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:9" ht="16.95" customHeight="1">
       <c r="A381" s="1" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B381" s="5">
         <f>IF(ISNA(VLOOKUP(H381,$A$2:$C$1028,3,1)),C381,VLOOKUP(H381,$A$2:$C$1028,3,1))</f>
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="C381" s="1">
-        <v>19</v>
+        <v>151</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>1099</v>
+        <v>303</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="F381" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A381,3,4)))</f>
-        <v>‧</v>
+        <v>⁳</v>
       </c>
       <c r="G381" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A381,3,4)))</f>
-        <v>‧</v>
+        <v>⁳</v>
       </c>
       <c r="H381" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="I381" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H381,3,4)))</f>
-        <v>1</v>
+        <v>E</v>
       </c>
     </row>
     <row r="382" spans="1:9" ht="16.95" customHeight="1">
       <c r="A382" s="1" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B382" s="5">
         <f>IF(ISNA(VLOOKUP(H382,$A$2:$C$1028,3,1)),C382,VLOOKUP(H382,$A$2:$C$1028,3,1))</f>
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="C382" s="1">
-        <v>151</v>
+        <v>15</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>303</v>
+        <v>1104</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="F382" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A382,3,4)))</f>
-        <v>⁳</v>
+        <v>₀</v>
       </c>
       <c r="G382" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A382,3,4)))</f>
-        <v>⁳</v>
+        <v>₀</v>
       </c>
       <c r="H382" s="1" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="I382" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H382,3,4)))</f>
-        <v>E</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383" spans="1:9" ht="16.95" customHeight="1">
       <c r="A383" s="1" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="B383" s="5">
         <f>IF(ISNA(VLOOKUP(H383,$A$2:$C$1028,3,1)),C383,VLOOKUP(H383,$A$2:$C$1028,3,1))</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C383" s="1">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="F383" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A383,3,4)))</f>
-        <v>₀</v>
+        <v>₁</v>
       </c>
       <c r="G383" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A383,3,4)))</f>
-        <v>₀</v>
+        <v>₁</v>
       </c>
       <c r="H383" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I383" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H383,3,4)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384" spans="1:9" ht="16.95" customHeight="1">
       <c r="A384" s="1" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B384" s="5">
         <f>IF(ISNA(VLOOKUP(H384,$A$2:$C$1028,3,1)),C384,VLOOKUP(H384,$A$2:$C$1028,3,1))</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C384" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="F384" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A384,3,4)))</f>
-        <v>₁</v>
+        <v>₂</v>
       </c>
       <c r="G384" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A384,3,4)))</f>
-        <v>₁</v>
+        <v>₂</v>
       </c>
       <c r="H384" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I384" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H384,3,4)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385" spans="1:9" ht="16.95" customHeight="1">
       <c r="A385" s="1" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="B385" s="5">
         <f>IF(ISNA(VLOOKUP(H385,$A$2:$C$1028,3,1)),C385,VLOOKUP(H385,$A$2:$C$1028,3,1))</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C385" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="F385" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A385,3,4)))</f>
-        <v>₂</v>
+        <v>₃</v>
       </c>
       <c r="G385" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A385,3,4)))</f>
-        <v>₂</v>
+        <v>₃</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I385" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H385,3,4)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386" spans="1:9" ht="16.95" customHeight="1">
       <c r="A386" s="1" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="B386" s="5">
         <f>IF(ISNA(VLOOKUP(H386,$A$2:$C$1028,3,1)),C386,VLOOKUP(H386,$A$2:$C$1028,3,1))</f>
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C386" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="F386" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A386,3,4)))</f>
-        <v>₃</v>
+        <v>₄</v>
       </c>
       <c r="G386" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A386,3,4)))</f>
-        <v>₃</v>
+        <v>₄</v>
       </c>
       <c r="H386" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I386" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H386,3,4)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="387" spans="1:9" ht="16.95" customHeight="1">
       <c r="A387" s="1" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="B387" s="5">
         <f>IF(ISNA(VLOOKUP(H387,$A$2:$C$1028,3,1)),C387,VLOOKUP(H387,$A$2:$C$1028,3,1))</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C387" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="F387" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A387,3,4)))</f>
-        <v>₄</v>
+        <v>₅</v>
       </c>
       <c r="G387" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A387,3,4)))</f>
-        <v>₄</v>
+        <v>₅</v>
       </c>
       <c r="H387" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I387" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H387,3,4)))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:9" ht="16.95" customHeight="1">
       <c r="A388" s="1" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="B388" s="5">
         <f>IF(ISNA(VLOOKUP(H388,$A$2:$C$1028,3,1)),C388,VLOOKUP(H388,$A$2:$C$1028,3,1))</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C388" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="F388" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A388,3,4)))</f>
-        <v>₅</v>
+        <v>₆</v>
       </c>
       <c r="G388" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A388,3,4)))</f>
-        <v>₅</v>
+        <v>₆</v>
       </c>
       <c r="H388" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I388" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H388,3,4)))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="389" spans="1:9" ht="16.95" customHeight="1">
       <c r="A389" s="1" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B389" s="5">
         <f>IF(ISNA(VLOOKUP(H389,$A$2:$C$1028,3,1)),C389,VLOOKUP(H389,$A$2:$C$1028,3,1))</f>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C389" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="F389" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A389,3,4)))</f>
-        <v>₆</v>
+        <v>₇</v>
       </c>
       <c r="G389" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A389,3,4)))</f>
-        <v>₆</v>
+        <v>₇</v>
       </c>
       <c r="H389" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I389" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H389,3,4)))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="390" spans="1:9" ht="16.95" customHeight="1">
       <c r="A390" s="1" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B390" s="5">
         <f>IF(ISNA(VLOOKUP(H390,$A$2:$C$1028,3,1)),C390,VLOOKUP(H390,$A$2:$C$1028,3,1))</f>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C390" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="F390" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A390,3,4)))</f>
-        <v>₇</v>
+        <v>₈</v>
       </c>
       <c r="G390" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A390,3,4)))</f>
-        <v>₇</v>
+        <v>₈</v>
       </c>
       <c r="H390" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I390" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H390,3,4)))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:9" ht="16.95" customHeight="1">
       <c r="A391" s="1" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="B391" s="5">
         <f>IF(ISNA(VLOOKUP(H391,$A$2:$C$1028,3,1)),C391,VLOOKUP(H391,$A$2:$C$1028,3,1))</f>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C391" s="1">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F391" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A391,3,4)))</f>
-        <v>₈</v>
+        <v>₉</v>
       </c>
       <c r="G391" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A391,3,4)))</f>
-        <v>₈</v>
+        <v>₉</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I391" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H391,3,4)))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="392" spans="1:9" ht="16.95" customHeight="1">
       <c r="A392" s="1" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="B392" s="5">
         <f>IF(ISNA(VLOOKUP(H392,$A$2:$C$1028,3,1)),C392,VLOOKUP(H392,$A$2:$C$1028,3,1))</f>
-        <v>54</v>
+        <v>517</v>
       </c>
       <c r="C392" s="1">
-        <v>56</v>
+        <v>519</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="F392" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A392,3,4)))</f>
-        <v>₉</v>
+        <v>₊</v>
       </c>
       <c r="G392" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A392,3,4)))</f>
-        <v>₉</v>
+        <v>₊</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="I392" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H392,3,4)))</f>
-        <v>9</v>
+        <v>+</v>
       </c>
     </row>
     <row r="393" spans="1:9" ht="16.95" customHeight="1">
       <c r="A393" s="1" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="B393" s="5">
         <f>IF(ISNA(VLOOKUP(H393,$A$2:$C$1028,3,1)),C393,VLOOKUP(H393,$A$2:$C$1028,3,1))</f>
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C393" s="1">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F393" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A393,3,4)))</f>
-        <v>₊</v>
+        <v>₋</v>
       </c>
       <c r="G393" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A393,3,4)))</f>
-        <v>₊</v>
+        <v>₋</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I393" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H393,3,4)))</f>
-        <v>+</v>
+        <v>-</v>
       </c>
     </row>
     <row r="394" spans="1:9" ht="16.95" customHeight="1">
       <c r="A394" s="1" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B394" s="5">
         <f>IF(ISNA(VLOOKUP(H394,$A$2:$C$1028,3,1)),C394,VLOOKUP(H394,$A$2:$C$1028,3,1))</f>
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C394" s="1">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1137</v>
+        <v>303</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="F394" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A394,3,4)))</f>
-        <v>₋</v>
+        <v>₏</v>
       </c>
       <c r="G394" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A394,3,4)))</f>
-        <v>₋</v>
+        <v>₏</v>
       </c>
       <c r="H394" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I394" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H394,3,4)))</f>
-        <v>-</v>
+        <v>×</v>
       </c>
     </row>
     <row r="395" spans="1:9" ht="16.95" customHeight="1">
       <c r="A395" s="1" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B395" s="5">
         <f>IF(ISNA(VLOOKUP(H395,$A$2:$C$1028,3,1)),C395,VLOOKUP(H395,$A$2:$C$1028,3,1))</f>
-        <v>526</v>
+        <v>635</v>
       </c>
       <c r="C395" s="1">
-        <v>531</v>
+        <v>636</v>
       </c>
       <c r="D395" s="2" t="s">
         <v>303</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="F395" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A395,3,4)))</f>
-        <v>₏</v>
+        <v>₞</v>
       </c>
       <c r="G395" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A395,3,4)))</f>
-        <v>₏</v>
+        <v>₞</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>47</v>
+        <v>1143</v>
       </c>
       <c r="I395" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H395,3,4)))</f>
-        <v>×</v>
+        <v>∞</v>
       </c>
     </row>
     <row r="396" spans="1:9" ht="16.95" customHeight="1">
       <c r="A396" s="1" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="B396" s="5">
         <f>IF(ISNA(VLOOKUP(H396,$A$2:$C$1028,3,1)),C396,VLOOKUP(H396,$A$2:$C$1028,3,1))</f>
         <v>635</v>
       </c>
       <c r="C396" s="1">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D396" s="2" t="s">
         <v>303</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="F396" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A396,3,4)))</f>
-        <v>₞</v>
+        <v>₟</v>
       </c>
       <c r="G396" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A396,3,4)))</f>
-        <v>₞</v>
+        <v>₟</v>
       </c>
       <c r="H396" s="1" t="s">
         <v>1143</v>
@@ -19859,127 +19862,127 @@
     </row>
     <row r="397" spans="1:9" ht="16.95" customHeight="1">
       <c r="A397" s="1" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B397" s="5">
         <f>IF(ISNA(VLOOKUP(H397,$A$2:$C$1028,3,1)),C397,VLOOKUP(H397,$A$2:$C$1028,3,1))</f>
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="C397" s="1">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>303</v>
+        <v>1147</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="F397" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A397,3,4)))</f>
-        <v>₟</v>
+        <v>€</v>
       </c>
       <c r="G397" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A397,3,4)))</f>
-        <v>₟</v>
+        <v>€</v>
       </c>
       <c r="H397" s="1" t="s">
-        <v>1143</v>
+        <v>24</v>
       </c>
       <c r="I397" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H397,3,4)))</f>
-        <v>∞</v>
+        <v>%</v>
       </c>
     </row>
     <row r="398" spans="1:9" ht="16.95" customHeight="1">
       <c r="A398" s="1" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B398" s="5">
         <f>IF(ISNA(VLOOKUP(H398,$A$2:$C$1028,3,1)),C398,VLOOKUP(H398,$A$2:$C$1028,3,1))</f>
-        <v>626</v>
+        <v>98</v>
       </c>
       <c r="C398" s="1">
-        <v>628</v>
+        <v>110</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="F398" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A398,3,4)))</f>
-        <v>€</v>
+        <v>ℂ</v>
       </c>
       <c r="G398" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A398,3,4)))</f>
-        <v>€</v>
+        <v>ℂ</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="I398" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H398,3,4)))</f>
-        <v>%</v>
+        <v>C</v>
       </c>
     </row>
     <row r="399" spans="1:9" ht="16.95" customHeight="1">
       <c r="A399" s="1" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="B399" s="5">
         <f>IF(ISNA(VLOOKUP(H399,$A$2:$C$1028,3,1)),C399,VLOOKUP(H399,$A$2:$C$1028,3,1))</f>
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C399" s="1">
-        <v>110</v>
+        <v>174</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="F399" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A399,3,4)))</f>
-        <v>ℂ</v>
+        <v>ℎ</v>
       </c>
       <c r="G399" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A399,3,4)))</f>
-        <v>ℂ</v>
+        <v>ℎ</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="I399" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H399,3,4)))</f>
-        <v>C</v>
+        <v>H</v>
       </c>
     </row>
     <row r="400" spans="1:9" ht="16.95" customHeight="1">
       <c r="A400" s="1" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="B400" s="5">
         <f>IF(ISNA(VLOOKUP(H400,$A$2:$C$1028,3,1)),C400,VLOOKUP(H400,$A$2:$C$1028,3,1))</f>
         <v>172</v>
       </c>
       <c r="C400" s="1">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="F400" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A400,3,4)))</f>
-        <v>ℎ</v>
+        <v>ℏ</v>
       </c>
       <c r="G400" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A400,3,4)))</f>
-        <v>ℎ</v>
+        <v>ℏ</v>
       </c>
       <c r="H400" s="1" t="s">
         <v>141</v>
@@ -19991,226 +19994,226 @@
     </row>
     <row r="401" spans="1:9" ht="16.95" customHeight="1">
       <c r="A401" s="1" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B401" s="5">
         <f>IF(ISNA(VLOOKUP(H401,$A$2:$C$1028,3,1)),C401,VLOOKUP(H401,$A$2:$C$1028,3,1))</f>
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C401" s="1">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="F401" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A401,3,4)))</f>
-        <v>ℏ</v>
+        <v>ℐ</v>
       </c>
       <c r="G401" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A401,3,4)))</f>
-        <v>ℏ</v>
+        <v>ℐ</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I401" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H401,3,4)))</f>
-        <v>H</v>
+        <v>I</v>
       </c>
     </row>
     <row r="402" spans="1:9" ht="16.95" customHeight="1">
       <c r="A402" s="1" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="B402" s="5">
         <f>IF(ISNA(VLOOKUP(H402,$A$2:$C$1028,3,1)),C402,VLOOKUP(H402,$A$2:$C$1028,3,1))</f>
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="C402" s="1">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="F402" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A402,3,4)))</f>
-        <v>ℐ</v>
+        <v>ℓ</v>
       </c>
       <c r="G402" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A402,3,4)))</f>
-        <v>ℐ</v>
+        <v>ℓ</v>
       </c>
       <c r="H402" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I402" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H402,3,4)))</f>
-        <v>I</v>
+        <v>L</v>
       </c>
     </row>
     <row r="403" spans="1:9" ht="16.95" customHeight="1">
       <c r="A403" s="1" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B403" s="5">
         <f>IF(ISNA(VLOOKUP(H403,$A$2:$C$1028,3,1)),C403,VLOOKUP(H403,$A$2:$C$1028,3,1))</f>
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="C403" s="1">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="F403" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A403,3,4)))</f>
-        <v>ℓ</v>
+        <v>ℕ</v>
       </c>
       <c r="G403" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A403,3,4)))</f>
-        <v>ℓ</v>
+        <v>ℕ</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I403" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H403,3,4)))</f>
-        <v>L</v>
+        <v>N</v>
       </c>
     </row>
     <row r="404" spans="1:9" ht="16.95" customHeight="1">
       <c r="A404" s="1" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="B404" s="5">
         <f>IF(ISNA(VLOOKUP(H404,$A$2:$C$1028,3,1)),C404,VLOOKUP(H404,$A$2:$C$1028,3,1))</f>
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="C404" s="1">
-        <v>253</v>
+        <v>293</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="F404" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A404,3,4)))</f>
-        <v>ℕ</v>
+        <v>ℚ</v>
       </c>
       <c r="G404" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A404,3,4)))</f>
-        <v>ℕ</v>
+        <v>ℚ</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="I404" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H404,3,4)))</f>
-        <v>N</v>
+        <v>Q</v>
       </c>
     </row>
     <row r="405" spans="1:9" ht="16.95" customHeight="1">
       <c r="A405" s="1" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="B405" s="5">
         <f>IF(ISNA(VLOOKUP(H405,$A$2:$C$1028,3,1)),C405,VLOOKUP(H405,$A$2:$C$1028,3,1))</f>
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C405" s="1">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="F405" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A405,3,4)))</f>
-        <v>ℚ</v>
+        <v>ℝ</v>
       </c>
       <c r="G405" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A405,3,4)))</f>
-        <v>ℚ</v>
+        <v>ℝ</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I405" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H405,3,4)))</f>
-        <v>Q</v>
+        <v>R</v>
       </c>
     </row>
     <row r="406" spans="1:9" ht="16.95" customHeight="1">
       <c r="A406" s="1" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B406" s="5">
         <f>IF(ISNA(VLOOKUP(H406,$A$2:$C$1028,3,1)),C406,VLOOKUP(H406,$A$2:$C$1028,3,1))</f>
-        <v>294</v>
+        <v>402</v>
       </c>
       <c r="C406" s="1">
-        <v>305</v>
+        <v>414</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="F406" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A406,3,4)))</f>
-        <v>ℝ</v>
+        <v>ℤ</v>
       </c>
       <c r="G406" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A406,3,4)))</f>
-        <v>ℝ</v>
+        <v>ℤ</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="I406" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H406,3,4)))</f>
-        <v>R</v>
+        <v>Z</v>
       </c>
     </row>
     <row r="407" spans="1:9" ht="16.95" customHeight="1">
       <c r="A407" s="1" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="B407" s="5">
         <f>IF(ISNA(VLOOKUP(H407,$A$2:$C$1028,3,1)),C407,VLOOKUP(H407,$A$2:$C$1028,3,1))</f>
         <v>402</v>
       </c>
       <c r="C407" s="1">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="F407" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A407,3,4)))</f>
-        <v>ℤ</v>
+        <v>℥</v>
       </c>
       <c r="G407" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A407,3,4)))</f>
-        <v>ℤ</v>
+        <v>℥</v>
       </c>
       <c r="H407" s="1" t="s">
         <v>195</v>
@@ -20222,1317 +20225,1317 @@
     </row>
     <row r="408" spans="1:9" ht="16.95" customHeight="1">
       <c r="A408" s="1" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="B408" s="5">
         <f>IF(ISNA(VLOOKUP(H408,$A$2:$C$1028,3,1)),C408,VLOOKUP(H408,$A$2:$C$1028,3,1))</f>
-        <v>402</v>
+        <v>319</v>
       </c>
       <c r="C408" s="1">
-        <v>415</v>
+        <v>331</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>1177</v>
+        <v>303</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="F408" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A408,3,4)))</f>
-        <v>℥</v>
+        <v>ℸ</v>
       </c>
       <c r="G408" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A408,3,4)))</f>
-        <v>℥</v>
+        <v>ℸ</v>
       </c>
       <c r="H408" s="1" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="I408" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H408,3,4)))</f>
-        <v>Z</v>
+        <v>T</v>
       </c>
     </row>
     <row r="409" spans="1:9" ht="16.95" customHeight="1">
       <c r="A409" s="1" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B409" s="5">
         <f>IF(ISNA(VLOOKUP(H409,$A$2:$C$1028,3,1)),C409,VLOOKUP(H409,$A$2:$C$1028,3,1))</f>
-        <v>319</v>
+        <v>113</v>
       </c>
       <c r="C409" s="1">
-        <v>331</v>
+        <v>125</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>303</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="F409" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A409,3,4)))</f>
-        <v>ℸ</v>
+        <v>ⅅ</v>
       </c>
       <c r="G409" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A409,3,4)))</f>
-        <v>ℸ</v>
+        <v>ⅅ</v>
       </c>
       <c r="H409" s="1" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="I409" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H409,3,4)))</f>
-        <v>T</v>
+        <v>D</v>
       </c>
     </row>
     <row r="410" spans="1:9" ht="16.95" customHeight="1">
       <c r="A410" s="1" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B410" s="5">
         <f>IF(ISNA(VLOOKUP(H410,$A$2:$C$1028,3,1)),C410,VLOOKUP(H410,$A$2:$C$1028,3,1))</f>
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C410" s="1">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>303</v>
+        <v>1184</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="F410" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A410,3,4)))</f>
-        <v>ⅅ</v>
+        <v>ⅇ</v>
       </c>
       <c r="G410" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A410,3,4)))</f>
-        <v>ⅅ</v>
+        <v>ⅇ</v>
       </c>
       <c r="H410" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I410" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H410,3,4)))</f>
-        <v>D</v>
+        <v>E</v>
       </c>
     </row>
     <row r="411" spans="1:9" ht="16.95" customHeight="1">
       <c r="A411" s="1" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="B411" s="5">
         <f>IF(ISNA(VLOOKUP(H411,$A$2:$C$1028,3,1)),C411,VLOOKUP(H411,$A$2:$C$1028,3,1))</f>
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="C411" s="1">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="F411" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A411,3,4)))</f>
-        <v>ⅇ</v>
+        <v>ⅈ</v>
       </c>
       <c r="G411" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A411,3,4)))</f>
-        <v>ⅇ</v>
+        <v>ⅈ</v>
       </c>
       <c r="H411" s="1" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="I411" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H411,3,4)))</f>
-        <v>E</v>
+        <v>I</v>
       </c>
     </row>
     <row r="412" spans="1:9" ht="16.95" customHeight="1">
       <c r="A412" s="1" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="B412" s="5">
         <f>IF(ISNA(VLOOKUP(H412,$A$2:$C$1028,3,1)),C412,VLOOKUP(H412,$A$2:$C$1028,3,1))</f>
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C412" s="1">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="F412" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A412,3,4)))</f>
-        <v>ⅈ</v>
+        <v>ⅉ</v>
       </c>
       <c r="G412" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A412,3,4)))</f>
-        <v>ⅈ</v>
+        <v>ⅉ</v>
       </c>
       <c r="H412" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I412" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H412,3,4)))</f>
-        <v>I</v>
+        <v>J</v>
       </c>
     </row>
     <row r="413" spans="1:9" ht="16.95" customHeight="1">
       <c r="A413" s="1" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="B413" s="5">
         <f>IF(ISNA(VLOOKUP(H413,$A$2:$C$1028,3,1)),C413,VLOOKUP(H413,$A$2:$C$1028,3,1))</f>
-        <v>206</v>
+        <v>11</v>
       </c>
       <c r="C413" s="1">
-        <v>213</v>
+        <v>14</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="F413" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A413,3,4)))</f>
-        <v>ⅉ</v>
+        <v>Ⅰ</v>
       </c>
       <c r="G413" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A413,3,4)))</f>
-        <v>ⅉ</v>
+        <v>Ⅰ</v>
       </c>
       <c r="H413" s="1" t="s">
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="I413" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H413,3,4)))</f>
-        <v>J</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="1:9" ht="16.95" customHeight="1">
       <c r="A414" s="1" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="B414" s="5">
         <f>IF(ISNA(VLOOKUP(H414,$A$2:$C$1028,3,1)),C414,VLOOKUP(H414,$A$2:$C$1028,3,1))</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C414" s="1">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="F414" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A414,3,4)))</f>
-        <v>Ⅰ</v>
+        <v>Ⅱ</v>
       </c>
       <c r="G414" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A414,3,4)))</f>
-        <v>Ⅰ</v>
+        <v>Ⅱ</v>
       </c>
       <c r="H414" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I414" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H414,3,4)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415" spans="1:9" ht="16.95" customHeight="1">
       <c r="A415" s="1" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="B415" s="5">
         <f>IF(ISNA(VLOOKUP(H415,$A$2:$C$1028,3,1)),C415,VLOOKUP(H415,$A$2:$C$1028,3,1))</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C415" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="F415" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A415,3,4)))</f>
-        <v>Ⅱ</v>
+        <v>Ⅲ</v>
       </c>
       <c r="G415" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A415,3,4)))</f>
-        <v>Ⅱ</v>
+        <v>Ⅲ</v>
       </c>
       <c r="H415" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I415" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H415,3,4)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416" spans="1:9" ht="16.95" customHeight="1">
       <c r="A416" s="1" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="B416" s="5">
         <f>IF(ISNA(VLOOKUP(H416,$A$2:$C$1028,3,1)),C416,VLOOKUP(H416,$A$2:$C$1028,3,1))</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C416" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="F416" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A416,3,4)))</f>
-        <v>Ⅲ</v>
+        <v>Ⅳ</v>
       </c>
       <c r="G416" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A416,3,4)))</f>
-        <v>Ⅲ</v>
+        <v>Ⅳ</v>
       </c>
       <c r="H416" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I416" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H416,3,4)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417" spans="1:9" ht="16.95" customHeight="1">
       <c r="A417" s="1" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="B417" s="5">
         <f>IF(ISNA(VLOOKUP(H417,$A$2:$C$1028,3,1)),C417,VLOOKUP(H417,$A$2:$C$1028,3,1))</f>
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C417" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="F417" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A417,3,4)))</f>
-        <v>Ⅳ</v>
+        <v>Ⅴ</v>
       </c>
       <c r="G417" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A417,3,4)))</f>
-        <v>Ⅳ</v>
+        <v>Ⅴ</v>
       </c>
       <c r="H417" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I417" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H417,3,4)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="418" spans="1:9" ht="16.95" customHeight="1">
       <c r="A418" s="1" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="B418" s="5">
         <f>IF(ISNA(VLOOKUP(H418,$A$2:$C$1028,3,1)),C418,VLOOKUP(H418,$A$2:$C$1028,3,1))</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C418" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="F418" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A418,3,4)))</f>
-        <v>Ⅴ</v>
+        <v>Ⅵ</v>
       </c>
       <c r="G418" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A418,3,4)))</f>
-        <v>Ⅴ</v>
+        <v>Ⅵ</v>
       </c>
       <c r="H418" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I418" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H418,3,4)))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="419" spans="1:9" ht="16.95" customHeight="1">
       <c r="A419" s="1" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="B419" s="5">
         <f>IF(ISNA(VLOOKUP(H419,$A$2:$C$1028,3,1)),C419,VLOOKUP(H419,$A$2:$C$1028,3,1))</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C419" s="1">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="F419" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A419,3,4)))</f>
-        <v>Ⅵ</v>
+        <v>Ⅶ</v>
       </c>
       <c r="G419" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A419,3,4)))</f>
-        <v>Ⅵ</v>
+        <v>Ⅶ</v>
       </c>
       <c r="H419" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I419" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H419,3,4)))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="420" spans="1:9" ht="16.95" customHeight="1">
       <c r="A420" s="1" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="B420" s="5">
         <f>IF(ISNA(VLOOKUP(H420,$A$2:$C$1028,3,1)),C420,VLOOKUP(H420,$A$2:$C$1028,3,1))</f>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C420" s="1">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="F420" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A420,3,4)))</f>
-        <v>Ⅶ</v>
+        <v>Ⅷ</v>
       </c>
       <c r="G420" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A420,3,4)))</f>
-        <v>Ⅶ</v>
+        <v>Ⅷ</v>
       </c>
       <c r="H420" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I420" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H420,3,4)))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="421" spans="1:9" ht="16.95" customHeight="1">
       <c r="A421" s="1" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="B421" s="5">
         <f>IF(ISNA(VLOOKUP(H421,$A$2:$C$1028,3,1)),C421,VLOOKUP(H421,$A$2:$C$1028,3,1))</f>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C421" s="1">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="F421" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A421,3,4)))</f>
-        <v>Ⅷ</v>
+        <v>Ⅸ</v>
       </c>
       <c r="G421" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A421,3,4)))</f>
-        <v>Ⅷ</v>
+        <v>Ⅸ</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I421" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H421,3,4)))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="422" spans="1:9" ht="16.95" customHeight="1">
       <c r="A422" s="1" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B422" s="5">
         <f>IF(ISNA(VLOOKUP(H422,$A$2:$C$1028,3,1)),C422,VLOOKUP(H422,$A$2:$C$1028,3,1))</f>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C422" s="1">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="F422" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A422,3,4)))</f>
-        <v>Ⅸ</v>
+        <v>Ⅹ</v>
       </c>
       <c r="G422" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A422,3,4)))</f>
-        <v>Ⅸ</v>
+        <v>Ⅹ</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I422" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H422,3,4)))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="423" spans="1:9" ht="16.95" customHeight="1">
       <c r="A423" s="1" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="B423" s="5">
         <f>IF(ISNA(VLOOKUP(H423,$A$2:$C$1028,3,1)),C423,VLOOKUP(H423,$A$2:$C$1028,3,1))</f>
-        <v>54</v>
+        <v>517</v>
       </c>
       <c r="C423" s="1">
-        <v>55</v>
+        <v>518</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="F423" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A423,3,4)))</f>
-        <v>Ⅹ</v>
+        <v>Ⅺ</v>
       </c>
       <c r="G423" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A423,3,4)))</f>
-        <v>Ⅹ</v>
+        <v>Ⅺ</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="I423" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H423,3,4)))</f>
-        <v>9</v>
+        <v>+</v>
       </c>
     </row>
     <row r="424" spans="1:9" ht="16.95" customHeight="1">
       <c r="A424" s="1" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B424" s="5">
         <f>IF(ISNA(VLOOKUP(H424,$A$2:$C$1028,3,1)),C424,VLOOKUP(H424,$A$2:$C$1028,3,1))</f>
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C424" s="1">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="F424" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A424,3,4)))</f>
-        <v>Ⅺ</v>
+        <v>Ⅻ</v>
       </c>
       <c r="G424" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A424,3,4)))</f>
-        <v>Ⅺ</v>
+        <v>Ⅻ</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I424" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H424,3,4)))</f>
-        <v>+</v>
+        <v>-</v>
       </c>
     </row>
     <row r="425" spans="1:9" ht="16.95" customHeight="1">
       <c r="A425" s="1" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="B425" s="5">
         <f>IF(ISNA(VLOOKUP(H425,$A$2:$C$1028,3,1)),C425,VLOOKUP(H425,$A$2:$C$1028,3,1))</f>
-        <v>521</v>
+        <v>578</v>
       </c>
       <c r="C425" s="1">
-        <v>522</v>
+        <v>578</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="F425" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A425,3,4)))</f>
-        <v>Ⅻ</v>
+        <v>←</v>
       </c>
       <c r="G425" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A425,3,4)))</f>
-        <v>Ⅻ</v>
+        <v>←</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>55</v>
+        <v>1228</v>
       </c>
       <c r="I425" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H425,3,4)))</f>
-        <v>-</v>
+        <v>←</v>
       </c>
     </row>
     <row r="426" spans="1:9" ht="16.95" customHeight="1">
       <c r="A426" s="1" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B426" s="5">
         <f>IF(ISNA(VLOOKUP(H426,$A$2:$C$1028,3,1)),C426,VLOOKUP(H426,$A$2:$C$1028,3,1))</f>
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C426" s="1">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="F426" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A426,3,4)))</f>
-        <v>←</v>
+        <v>↑</v>
       </c>
       <c r="G426" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A426,3,4)))</f>
-        <v>←</v>
+        <v>↑</v>
       </c>
       <c r="H426" s="1" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="I426" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H426,3,4)))</f>
-        <v>←</v>
+        <v>↑</v>
       </c>
     </row>
     <row r="427" spans="1:9" ht="16.95" customHeight="1">
       <c r="A427" s="1" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="B427" s="5">
         <f>IF(ISNA(VLOOKUP(H427,$A$2:$C$1028,3,1)),C427,VLOOKUP(H427,$A$2:$C$1028,3,1))</f>
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C427" s="1">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="F427" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A427,3,4)))</f>
-        <v>↑</v>
+        <v>→</v>
       </c>
       <c r="G427" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A427,3,4)))</f>
-        <v>↑</v>
+        <v>→</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="I427" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H427,3,4)))</f>
-        <v>↑</v>
+        <v>→</v>
       </c>
     </row>
     <row r="428" spans="1:9" ht="16.95" customHeight="1">
       <c r="A428" s="1" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="B428" s="5">
         <f>IF(ISNA(VLOOKUP(H428,$A$2:$C$1028,3,1)),C428,VLOOKUP(H428,$A$2:$C$1028,3,1))</f>
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="C428" s="1">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="F428" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A428,3,4)))</f>
-        <v>→</v>
+        <v>↓</v>
       </c>
       <c r="G428" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A428,3,4)))</f>
-        <v>→</v>
+        <v>↓</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="I428" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H428,3,4)))</f>
-        <v>→</v>
+        <v>↓</v>
       </c>
     </row>
     <row r="429" spans="1:9" ht="16.95" customHeight="1">
       <c r="A429" s="1" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="B429" s="5">
         <f>IF(ISNA(VLOOKUP(H429,$A$2:$C$1028,3,1)),C429,VLOOKUP(H429,$A$2:$C$1028,3,1))</f>
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C429" s="1">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="F429" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A429,3,4)))</f>
-        <v>↓</v>
+        <v>↔</v>
       </c>
       <c r="G429" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A429,3,4)))</f>
-        <v>↓</v>
+        <v>↔</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="I429" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H429,3,4)))</f>
-        <v>↓</v>
+        <v>⇄</v>
       </c>
     </row>
     <row r="430" spans="1:9" ht="16.95" customHeight="1">
       <c r="A430" s="1" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="B430" s="5">
         <f>IF(ISNA(VLOOKUP(H430,$A$2:$C$1028,3,1)),C430,VLOOKUP(H430,$A$2:$C$1028,3,1))</f>
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C430" s="1">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="F430" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A430,3,4)))</f>
-        <v>↔</v>
+        <v>↕</v>
       </c>
       <c r="G430" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A430,3,4)))</f>
-        <v>↔</v>
+        <v>↕</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="I430" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H430,3,4)))</f>
-        <v>⇄</v>
+        <v>↕</v>
       </c>
     </row>
     <row r="431" spans="1:9" ht="16.95" customHeight="1">
       <c r="A431" s="1" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="B431" s="5">
         <f>IF(ISNA(VLOOKUP(H431,$A$2:$C$1028,3,1)),C431,VLOOKUP(H431,$A$2:$C$1028,3,1))</f>
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="C431" s="1">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="F431" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A431,3,4)))</f>
-        <v>↕</v>
+        <v>↵</v>
       </c>
       <c r="G431" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A431,3,4)))</f>
-        <v>↕</v>
+        <v>↵</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="I431" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H431,3,4)))</f>
-        <v>↕</v>
+        <v>←</v>
       </c>
     </row>
     <row r="432" spans="1:9" ht="16.95" customHeight="1">
       <c r="A432" s="1" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="B432" s="5">
         <f>IF(ISNA(VLOOKUP(H432,$A$2:$C$1028,3,1)),C432,VLOOKUP(H432,$A$2:$C$1028,3,1))</f>
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C432" s="1">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="F432" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A432,3,4)))</f>
-        <v>↵</v>
+        <v>⇀</v>
       </c>
       <c r="G432" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A432,3,4)))</f>
-        <v>↵</v>
+        <v>⇀</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="I432" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H432,3,4)))</f>
-        <v>←</v>
+        <v>→</v>
       </c>
     </row>
     <row r="433" spans="1:11" ht="16.95" customHeight="1">
       <c r="A433" s="1" t="s">
-        <v>1250</v>
+        <v>1243</v>
       </c>
       <c r="B433" s="5">
         <f>IF(ISNA(VLOOKUP(H433,$A$2:$C$1028,3,1)),C433,VLOOKUP(H433,$A$2:$C$1028,3,1))</f>
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="C433" s="1">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>1252</v>
+        <v>1242</v>
       </c>
       <c r="F433" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A433,3,4)))</f>
-        <v>⇀</v>
+        <v>⇄</v>
       </c>
       <c r="G433" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A433,3,4)))</f>
-        <v>⇀</v>
+        <v>⇄</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>1234</v>
+        <v>1243</v>
       </c>
       <c r="I433" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H433,3,4)))</f>
-        <v>→</v>
+        <v>⇄</v>
       </c>
     </row>
     <row r="434" spans="1:11" ht="16.95" customHeight="1">
       <c r="A434" s="1" t="s">
-        <v>1243</v>
+        <v>1254</v>
       </c>
       <c r="B434" s="5">
         <f>IF(ISNA(VLOOKUP(H434,$A$2:$C$1028,3,1)),C434,VLOOKUP(H434,$A$2:$C$1028,3,1))</f>
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C434" s="1">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>1242</v>
+        <v>1256</v>
       </c>
       <c r="F434" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A434,3,4)))</f>
-        <v>⇄</v>
+        <v>⇉</v>
       </c>
       <c r="G434" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A434,3,4)))</f>
-        <v>⇄</v>
+        <v>⇉</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
       <c r="I434" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H434,3,4)))</f>
-        <v>⇄</v>
+        <v>↑</v>
       </c>
     </row>
     <row r="435" spans="1:11" ht="16.95" customHeight="1">
       <c r="A435" s="1" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="B435" s="5">
         <f>IF(ISNA(VLOOKUP(H435,$A$2:$C$1028,3,1)),C435,VLOOKUP(H435,$A$2:$C$1028,3,1))</f>
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C435" s="1">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="F435" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A435,3,4)))</f>
-        <v>⇉</v>
+        <v>⇋</v>
       </c>
       <c r="G435" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A435,3,4)))</f>
-        <v>⇉</v>
+        <v>⇋</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="I435" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H435,3,4)))</f>
-        <v>↑</v>
+        <v>↓</v>
       </c>
     </row>
     <row r="436" spans="1:11" ht="16.95" customHeight="1">
       <c r="A436" s="1" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="B436" s="5">
         <f>IF(ISNA(VLOOKUP(H436,$A$2:$C$1028,3,1)),C436,VLOOKUP(H436,$A$2:$C$1028,3,1))</f>
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="C436" s="1">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="F436" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A436,3,4)))</f>
-        <v>⇋</v>
+        <v>⇌</v>
       </c>
       <c r="G436" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A436,3,4)))</f>
-        <v>⇋</v>
+        <v>⇌</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>1237</v>
+        <v>1260</v>
       </c>
       <c r="I436" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H436,3,4)))</f>
-        <v>↓</v>
+        <v>⇌</v>
       </c>
     </row>
     <row r="437" spans="1:11" ht="16.95" customHeight="1">
       <c r="A437" s="1" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="B437" s="5">
         <f>IF(ISNA(VLOOKUP(H437,$A$2:$C$1028,3,1)),C437,VLOOKUP(H437,$A$2:$C$1028,3,1))</f>
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="C437" s="1">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="F437" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A437,3,4)))</f>
-        <v>⇌</v>
+        <v>⇒</v>
       </c>
       <c r="G437" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A437,3,4)))</f>
-        <v>⇌</v>
+        <v>⇒</v>
       </c>
       <c r="H437" s="1" t="s">
-        <v>1260</v>
+        <v>1234</v>
       </c>
       <c r="I437" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H437,3,4)))</f>
-        <v>⇌</v>
+        <v>→</v>
       </c>
     </row>
     <row r="438" spans="1:11" ht="16.95" customHeight="1">
       <c r="A438" s="1" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B438" s="5">
         <f>IF(ISNA(VLOOKUP(H438,$A$2:$C$1028,3,1)),C438,VLOOKUP(H438,$A$2:$C$1028,3,1))</f>
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="C438" s="1">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="F438" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A438,3,4)))</f>
-        <v>⇒</v>
+        <v>⇔</v>
       </c>
       <c r="G438" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A438,3,4)))</f>
-        <v>⇒</v>
+        <v>⇔</v>
       </c>
       <c r="H438" s="1" t="s">
-        <v>1234</v>
+        <v>1243</v>
       </c>
       <c r="I438" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H438,3,4)))</f>
-        <v>→</v>
+        <v>⇄</v>
       </c>
     </row>
     <row r="439" spans="1:11" ht="16.95" customHeight="1">
       <c r="A439" s="1" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="B439" s="5">
         <f>IF(ISNA(VLOOKUP(H439,$A$2:$C$1028,3,1)),C439,VLOOKUP(H439,$A$2:$C$1028,3,1))</f>
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="C439" s="1">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1268</v>
+        <v>1229</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>1269</v>
+        <v>1230</v>
       </c>
       <c r="F439" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A439,3,4)))</f>
-        <v>⇔</v>
+        <v>⇠</v>
       </c>
       <c r="G439" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A439,3,4)))</f>
-        <v>⇔</v>
+        <v>⇠</v>
       </c>
       <c r="H439" s="1" t="s">
-        <v>1243</v>
+        <v>1228</v>
       </c>
       <c r="I439" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H439,3,4)))</f>
-        <v>⇄</v>
+        <v>←</v>
       </c>
     </row>
     <row r="440" spans="1:11" ht="16.95" customHeight="1">
       <c r="A440" s="1" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B440" s="5">
         <f>IF(ISNA(VLOOKUP(H440,$A$2:$C$1028,3,1)),C440,VLOOKUP(H440,$A$2:$C$1028,3,1))</f>
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C440" s="1">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="F440" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A440,3,4)))</f>
-        <v>⇠</v>
+        <v>⇡</v>
       </c>
       <c r="G440" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A440,3,4)))</f>
-        <v>⇠</v>
+        <v>⇡</v>
       </c>
       <c r="H440" s="1" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="I440" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H440,3,4)))</f>
-        <v>←</v>
+        <v>↑</v>
       </c>
     </row>
     <row r="441" spans="1:11" ht="16.95" customHeight="1">
       <c r="A441" s="1" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B441" s="5">
         <f>IF(ISNA(VLOOKUP(H441,$A$2:$C$1028,3,1)),C441,VLOOKUP(H441,$A$2:$C$1028,3,1))</f>
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C441" s="1">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="F441" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A441,3,4)))</f>
-        <v>⇡</v>
+        <v>⇢</v>
       </c>
       <c r="G441" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A441,3,4)))</f>
-        <v>⇡</v>
+        <v>⇢</v>
       </c>
       <c r="H441" s="1" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="I441" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H441,3,4)))</f>
-        <v>↑</v>
+        <v>→</v>
       </c>
     </row>
     <row r="442" spans="1:11" s="16" customFormat="1" ht="16.95" customHeight="1">
       <c r="A442" s="1" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B442" s="5">
         <f>IF(ISNA(VLOOKUP(H442,$A$2:$C$1028,3,1)),C442,VLOOKUP(H442,$A$2:$C$1028,3,1))</f>
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="C442" s="1">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="F442" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A442,3,4)))</f>
-        <v>⇢</v>
+        <v>⇣</v>
       </c>
       <c r="G442" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A442,3,4)))</f>
-        <v>⇢</v>
+        <v>⇣</v>
       </c>
       <c r="H442" s="1" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="I442" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H442,3,4)))</f>
-        <v>→</v>
+        <v>↓</v>
       </c>
       <c r="J442" s="4"/>
       <c r="K442" s="2"/>
     </row>
     <row r="443" spans="1:11" ht="16.95" customHeight="1">
       <c r="A443" s="1" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B443" s="5">
         <f>IF(ISNA(VLOOKUP(H443,$A$2:$C$1028,3,1)),C443,VLOOKUP(H443,$A$2:$C$1028,3,1))</f>
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="C443" s="1">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1238</v>
+        <v>1275</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>1239</v>
+        <v>1276</v>
       </c>
       <c r="F443" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A443,3,4)))</f>
-        <v>⇣</v>
+        <v>⇧</v>
       </c>
       <c r="G443" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A443,3,4)))</f>
-        <v>⇣</v>
+        <v>⇧</v>
       </c>
       <c r="H443" s="1" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="I443" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H443,3,4)))</f>
-        <v>↓</v>
+        <v>↑</v>
       </c>
     </row>
     <row r="444" spans="1:11" ht="16.95" customHeight="1">
       <c r="A444" s="1" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B444" s="5">
         <f>IF(ISNA(VLOOKUP(H444,$A$2:$C$1028,3,1)),C444,VLOOKUP(H444,$A$2:$C$1028,3,1))</f>
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C444" s="1">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="F444" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A444,3,4)))</f>
-        <v>⇧</v>
+        <v>⇩</v>
       </c>
       <c r="G444" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A444,3,4)))</f>
-        <v>⇧</v>
+        <v>⇩</v>
       </c>
       <c r="H444" s="1" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="I444" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H444,3,4)))</f>
-        <v>↑</v>
+        <v>↓</v>
       </c>
     </row>
     <row r="445" spans="1:11" ht="16.95" customHeight="1">
       <c r="A445" s="1" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B445" s="5">
         <f>IF(ISNA(VLOOKUP(H445,$A$2:$C$1028,3,1)),C445,VLOOKUP(H445,$A$2:$C$1028,3,1))</f>
-        <v>589</v>
+        <v>98</v>
       </c>
       <c r="C445" s="1">
-        <v>592</v>
+        <v>111</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="F445" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A445,3,4)))</f>
-        <v>⇩</v>
+        <v>∁</v>
       </c>
       <c r="G445" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A445,3,4)))</f>
-        <v>⇩</v>
+        <v>∁</v>
       </c>
       <c r="H445" s="1" t="s">
-        <v>1237</v>
+        <v>126</v>
       </c>
       <c r="I445" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H445,3,4)))</f>
-        <v>↓</v>
+        <v>C</v>
       </c>
     </row>
     <row r="446" spans="1:11" ht="16.95" customHeight="1">
       <c r="A446" s="1" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="B446" s="5">
         <f>IF(ISNA(VLOOKUP(H446,$A$2:$C$1028,3,1)),C446,VLOOKUP(H446,$A$2:$C$1028,3,1))</f>
-        <v>98</v>
+        <v>675</v>
       </c>
       <c r="C446" s="1">
-        <v>111</v>
+        <v>676</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="F446" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A446,3,4)))</f>
-        <v>∁</v>
+        <v>∂</v>
       </c>
       <c r="G446" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A446,3,4)))</f>
-        <v>∁</v>
-      </c>
-      <c r="H446" s="1" t="s">
-        <v>126</v>
+        <v>∂</v>
+      </c>
+      <c r="H446" s="20" t="s">
+        <v>1286</v>
       </c>
       <c r="I446" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H446,3,4)))</f>
-        <v>C</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="447" spans="1:11" ht="16.95" customHeight="1">
       <c r="A447" s="1" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="B447" s="5">
         <f>IF(ISNA(VLOOKUP(H447,$A$2:$C$1028,3,1)),C447,VLOOKUP(H447,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C447" s="1">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F447" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A447,3,4)))</f>
-        <v>∂</v>
+        <v>∃</v>
       </c>
       <c r="G447" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A447,3,4)))</f>
-        <v>∂</v>
+        <v>∃</v>
       </c>
       <c r="H447" s="20" t="s">
         <v>1286</v>
@@ -21544,28 +21547,28 @@
     </row>
     <row r="448" spans="1:11" ht="16.95" customHeight="1">
       <c r="A448" s="1" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B448" s="5">
         <f>IF(ISNA(VLOOKUP(H448,$A$2:$C$1028,3,1)),C448,VLOOKUP(H448,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C448" s="1">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="F448" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A448,3,4)))</f>
-        <v>∃</v>
+        <v>∄</v>
       </c>
       <c r="G448" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A448,3,4)))</f>
-        <v>∃</v>
+        <v>∄</v>
       </c>
       <c r="H448" s="20" t="s">
         <v>1286</v>
@@ -21577,28 +21580,28 @@
     </row>
     <row r="449" spans="1:9" ht="16.95" customHeight="1">
       <c r="A449" s="1" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="B449" s="5">
         <f>IF(ISNA(VLOOKUP(H449,$A$2:$C$1028,3,1)),C449,VLOOKUP(H449,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C449" s="1">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F449" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A449,3,4)))</f>
-        <v>∄</v>
+        <v>∅</v>
       </c>
       <c r="G449" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A449,3,4)))</f>
-        <v>∄</v>
+        <v>∅</v>
       </c>
       <c r="H449" s="20" t="s">
         <v>1286</v>
@@ -21610,28 +21613,28 @@
     </row>
     <row r="450" spans="1:9" ht="16.95" customHeight="1">
       <c r="A450" s="1" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="B450" s="5">
         <f>IF(ISNA(VLOOKUP(H450,$A$2:$C$1028,3,1)),C450,VLOOKUP(H450,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C450" s="1">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="F450" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A450,3,4)))</f>
-        <v>∅</v>
+        <v>∆</v>
       </c>
       <c r="G450" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A450,3,4)))</f>
-        <v>∅</v>
+        <v>∆</v>
       </c>
       <c r="H450" s="20" t="s">
         <v>1286</v>
@@ -21643,28 +21646,28 @@
     </row>
     <row r="451" spans="1:9" ht="16.95" customHeight="1">
       <c r="A451" s="1" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="B451" s="5">
         <f>IF(ISNA(VLOOKUP(H451,$A$2:$C$1028,3,1)),C451,VLOOKUP(H451,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C451" s="1">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="F451" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A451,3,4)))</f>
-        <v>∆</v>
+        <v>∇</v>
       </c>
       <c r="G451" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A451,3,4)))</f>
-        <v>∆</v>
+        <v>∇</v>
       </c>
       <c r="H451" s="20" t="s">
         <v>1286</v>
@@ -21676,28 +21679,28 @@
     </row>
     <row r="452" spans="1:9" ht="16.95" customHeight="1">
       <c r="A452" s="1" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="B452" s="5">
         <f>IF(ISNA(VLOOKUP(H452,$A$2:$C$1028,3,1)),C452,VLOOKUP(H452,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C452" s="1">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="F452" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A452,3,4)))</f>
-        <v>∇</v>
+        <v>∈</v>
       </c>
       <c r="G452" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A452,3,4)))</f>
-        <v>∇</v>
+        <v>∈</v>
       </c>
       <c r="H452" s="20" t="s">
         <v>1286</v>
@@ -21709,28 +21712,28 @@
     </row>
     <row r="453" spans="1:9" ht="16.95" customHeight="1">
       <c r="A453" s="1" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="B453" s="5">
         <f>IF(ISNA(VLOOKUP(H453,$A$2:$C$1028,3,1)),C453,VLOOKUP(H453,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C453" s="1">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="F453" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A453,3,4)))</f>
-        <v>∈</v>
+        <v>∉</v>
       </c>
       <c r="G453" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A453,3,4)))</f>
-        <v>∈</v>
+        <v>∉</v>
       </c>
       <c r="H453" s="20" t="s">
         <v>1286</v>
@@ -21742,28 +21745,28 @@
     </row>
     <row r="454" spans="1:9" ht="16.95" customHeight="1">
       <c r="A454" s="1" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="B454" s="5">
         <f>IF(ISNA(VLOOKUP(H454,$A$2:$C$1028,3,1)),C454,VLOOKUP(H454,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C454" s="1">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="F454" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A454,3,4)))</f>
-        <v>∉</v>
+        <v>∋</v>
       </c>
       <c r="G454" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A454,3,4)))</f>
-        <v>∉</v>
+        <v>∋</v>
       </c>
       <c r="H454" s="20" t="s">
         <v>1286</v>
@@ -21775,28 +21778,28 @@
     </row>
     <row r="455" spans="1:9" ht="16.95" customHeight="1">
       <c r="A455" s="1" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="B455" s="5">
         <f>IF(ISNA(VLOOKUP(H455,$A$2:$C$1028,3,1)),C455,VLOOKUP(H455,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C455" s="1">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="F455" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A455,3,4)))</f>
-        <v>∋</v>
+        <v>∌</v>
       </c>
       <c r="G455" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A455,3,4)))</f>
-        <v>∋</v>
+        <v>∌</v>
       </c>
       <c r="H455" s="20" t="s">
         <v>1286</v>
@@ -21808,193 +21811,193 @@
     </row>
     <row r="456" spans="1:9" ht="16.95" customHeight="1">
       <c r="A456" s="1" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="B456" s="5">
         <f>IF(ISNA(VLOOKUP(H456,$A$2:$C$1028,3,1)),C456,VLOOKUP(H456,$A$2:$C$1028,3,1))</f>
-        <v>675</v>
+        <v>11</v>
       </c>
       <c r="C456" s="1">
-        <v>685</v>
+        <v>12</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="F456" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A456,3,4)))</f>
-        <v>∌</v>
+        <v>∎</v>
       </c>
       <c r="G456" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A456,3,4)))</f>
-        <v>∌</v>
-      </c>
-      <c r="H456" s="20" t="s">
-        <v>1286</v>
+        <v>∎</v>
+      </c>
+      <c r="H456" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="I456" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H456,3,4)))</f>
-        <v>Ɐ</v>
+        <v>0</v>
       </c>
     </row>
     <row r="457" spans="1:9" ht="16.95" customHeight="1">
       <c r="A457" s="1" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="B457" s="5">
         <f>IF(ISNA(VLOOKUP(H457,$A$2:$C$1028,3,1)),C457,VLOOKUP(H457,$A$2:$C$1028,3,1))</f>
-        <v>11</v>
+        <v>462</v>
       </c>
       <c r="C457" s="1">
-        <v>12</v>
+        <v>463</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="F457" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A457,3,4)))</f>
-        <v>∎</v>
+        <v>∏</v>
       </c>
       <c r="G457" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A457,3,4)))</f>
-        <v>∎</v>
+        <v>∏</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>67</v>
+        <v>881</v>
       </c>
       <c r="I457" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H457,3,4)))</f>
-        <v>0</v>
+        <v>Π</v>
       </c>
     </row>
     <row r="458" spans="1:9" ht="16.95" customHeight="1">
       <c r="A458" s="1" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="B458" s="5">
         <f>IF(ISNA(VLOOKUP(H458,$A$2:$C$1028,3,1)),C458,VLOOKUP(H458,$A$2:$C$1028,3,1))</f>
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C458" s="1">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="F458" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A458,3,4)))</f>
-        <v>∏</v>
+        <v>∑</v>
       </c>
       <c r="G458" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A458,3,4)))</f>
-        <v>∏</v>
+        <v>∑</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="I458" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H458,3,4)))</f>
-        <v>Π</v>
+        <v>Σ</v>
       </c>
     </row>
     <row r="459" spans="1:9" ht="16.95" customHeight="1">
       <c r="A459" s="1" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B459" s="5">
         <f>IF(ISNA(VLOOKUP(H459,$A$2:$C$1028,3,1)),C459,VLOOKUP(H459,$A$2:$C$1028,3,1))</f>
-        <v>470</v>
+        <v>521</v>
       </c>
       <c r="C459" s="1">
-        <v>473</v>
+        <v>524</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="F459" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A459,3,4)))</f>
-        <v>∑</v>
+        <v>∓</v>
       </c>
       <c r="G459" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A459,3,4)))</f>
-        <v>∑</v>
+        <v>∓</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>888</v>
+        <v>55</v>
       </c>
       <c r="I459" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H459,3,4)))</f>
-        <v>Σ</v>
+        <v>-</v>
       </c>
     </row>
     <row r="460" spans="1:9" ht="16.95" customHeight="1">
       <c r="A460" s="1" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="B460" s="5">
         <f>IF(ISNA(VLOOKUP(H460,$A$2:$C$1028,3,1)),C460,VLOOKUP(H460,$A$2:$C$1028,3,1))</f>
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C460" s="1">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="F460" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A460,3,4)))</f>
-        <v>∓</v>
+        <v>∘</v>
       </c>
       <c r="G460" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A460,3,4)))</f>
-        <v>∓</v>
+        <v>∘</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I460" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H460,3,4)))</f>
-        <v>-</v>
+        <v>×</v>
       </c>
     </row>
     <row r="461" spans="1:9" ht="16.95" customHeight="1">
       <c r="A461" s="1" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="B461" s="5">
         <f>IF(ISNA(VLOOKUP(H461,$A$2:$C$1028,3,1)),C461,VLOOKUP(H461,$A$2:$C$1028,3,1))</f>
         <v>526</v>
       </c>
       <c r="C461" s="1">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="F461" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A461,3,4)))</f>
-        <v>∘</v>
+        <v>∙</v>
       </c>
       <c r="G461" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A461,3,4)))</f>
-        <v>∘</v>
+        <v>∙</v>
       </c>
       <c r="H461" s="1" t="s">
         <v>47</v>
@@ -22006,259 +22009,259 @@
     </row>
     <row r="462" spans="1:9" ht="16.95" customHeight="1">
       <c r="A462" s="1" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="B462" s="5">
         <f>IF(ISNA(VLOOKUP(H462,$A$2:$C$1028,3,1)),C462,VLOOKUP(H462,$A$2:$C$1028,3,1))</f>
-        <v>526</v>
+        <v>633</v>
       </c>
       <c r="C462" s="1">
-        <v>528</v>
+        <v>633</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="F462" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A462,3,4)))</f>
-        <v>∙</v>
+        <v>√</v>
       </c>
       <c r="G462" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A462,3,4)))</f>
-        <v>∙</v>
+        <v>√</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>47</v>
+        <v>1332</v>
       </c>
       <c r="I462" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H462,3,4)))</f>
-        <v>×</v>
+        <v>√</v>
       </c>
     </row>
     <row r="463" spans="1:9" ht="16.95" customHeight="1">
       <c r="A463" s="1" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="B463" s="5">
         <f>IF(ISNA(VLOOKUP(H463,$A$2:$C$1028,3,1)),C463,VLOOKUP(H463,$A$2:$C$1028,3,1))</f>
-        <v>633</v>
+        <v>29</v>
       </c>
       <c r="C463" s="1">
-        <v>633</v>
+        <v>33</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="F463" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A463,3,4)))</f>
-        <v>√</v>
+        <v>∛</v>
       </c>
       <c r="G463" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A463,3,4)))</f>
-        <v>√</v>
+        <v>∛</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>1332</v>
+        <v>76</v>
       </c>
       <c r="I463" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H463,3,4)))</f>
-        <v>√</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464" spans="1:9" ht="16.95" customHeight="1">
       <c r="A464" s="1" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B464" s="5">
         <f>IF(ISNA(VLOOKUP(H464,$A$2:$C$1028,3,1)),C464,VLOOKUP(H464,$A$2:$C$1028,3,1))</f>
-        <v>29</v>
+        <v>376</v>
       </c>
       <c r="C464" s="1">
-        <v>33</v>
+        <v>386</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="F464" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A464,3,4)))</f>
-        <v>∛</v>
+        <v>∜</v>
       </c>
       <c r="G464" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A464,3,4)))</f>
-        <v>∛</v>
+        <v>∜</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="I464" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H464,3,4)))</f>
-        <v>3</v>
+        <v>X</v>
       </c>
     </row>
     <row r="465" spans="1:9" ht="16.95" customHeight="1">
       <c r="A465" s="1" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="B465" s="5">
         <f>IF(ISNA(VLOOKUP(H465,$A$2:$C$1028,3,1)),C465,VLOOKUP(H465,$A$2:$C$1028,3,1))</f>
-        <v>376</v>
+        <v>633</v>
       </c>
       <c r="C465" s="1">
-        <v>386</v>
+        <v>634</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="F465" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A465,3,4)))</f>
-        <v>∜</v>
+        <v>∝</v>
       </c>
       <c r="G465" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A465,3,4)))</f>
-        <v>∜</v>
+        <v>∝</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>189</v>
+        <v>1332</v>
       </c>
       <c r="I465" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H465,3,4)))</f>
-        <v>X</v>
+        <v>√</v>
       </c>
     </row>
     <row r="466" spans="1:9" ht="16.95" customHeight="1">
       <c r="A466" s="1" t="s">
-        <v>1341</v>
+        <v>1143</v>
       </c>
       <c r="B466" s="5">
         <f>IF(ISNA(VLOOKUP(H466,$A$2:$C$1028,3,1)),C466,VLOOKUP(H466,$A$2:$C$1028,3,1))</f>
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C466" s="1">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="F466" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A466,3,4)))</f>
-        <v>∝</v>
+        <v>∞</v>
       </c>
       <c r="G466" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A466,3,4)))</f>
-        <v>∝</v>
+        <v>∞</v>
       </c>
       <c r="H466" s="1" t="s">
-        <v>1332</v>
+        <v>1143</v>
       </c>
       <c r="I466" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H466,3,4)))</f>
-        <v>√</v>
+        <v>∞</v>
       </c>
     </row>
     <row r="467" spans="1:9" ht="16.95" customHeight="1">
       <c r="A467" s="1" t="s">
-        <v>1143</v>
+        <v>1346</v>
       </c>
       <c r="B467" s="5">
         <f>IF(ISNA(VLOOKUP(H467,$A$2:$C$1028,3,1)),C467,VLOOKUP(H467,$A$2:$C$1028,3,1))</f>
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="C467" s="1">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="F467" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A467,3,4)))</f>
-        <v>∞</v>
+        <v>∟</v>
       </c>
       <c r="G467" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A467,3,4)))</f>
-        <v>∞</v>
+        <v>∟</v>
       </c>
       <c r="H467" s="1" t="s">
-        <v>1143</v>
+        <v>1346</v>
       </c>
       <c r="I467" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H467,3,4)))</f>
-        <v>∞</v>
+        <v>∟</v>
       </c>
     </row>
     <row r="468" spans="1:9" ht="16.95" customHeight="1">
       <c r="A468" s="1" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="B468" s="5">
         <f>IF(ISNA(VLOOKUP(H468,$A$2:$C$1028,3,1)),C468,VLOOKUP(H468,$A$2:$C$1028,3,1))</f>
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C468" s="1">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="F468" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A468,3,4)))</f>
-        <v>∟</v>
+        <v>∠</v>
       </c>
       <c r="G468" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A468,3,4)))</f>
-        <v>∟</v>
+        <v>∠</v>
       </c>
       <c r="H468" s="1" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="I468" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H468,3,4)))</f>
-        <v>∟</v>
+        <v>∠</v>
       </c>
     </row>
     <row r="469" spans="1:9" ht="16.95" customHeight="1">
       <c r="A469" s="1" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="B469" s="5">
         <f>IF(ISNA(VLOOKUP(H469,$A$2:$C$1028,3,1)),C469,VLOOKUP(H469,$A$2:$C$1028,3,1))</f>
         <v>649</v>
       </c>
       <c r="C469" s="1">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="F469" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A469,3,4)))</f>
-        <v>∠</v>
+        <v>∡</v>
       </c>
       <c r="G469" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A469,3,4)))</f>
-        <v>∠</v>
+        <v>∡</v>
       </c>
       <c r="H469" s="1" t="s">
         <v>1349</v>
@@ -22270,28 +22273,28 @@
     </row>
     <row r="470" spans="1:9" ht="16.95" customHeight="1">
       <c r="A470" s="1" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="B470" s="5">
         <f>IF(ISNA(VLOOKUP(H470,$A$2:$C$1028,3,1)),C470,VLOOKUP(H470,$A$2:$C$1028,3,1))</f>
         <v>649</v>
       </c>
       <c r="C470" s="1">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="F470" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A470,3,4)))</f>
-        <v>∡</v>
+        <v>∢</v>
       </c>
       <c r="G470" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A470,3,4)))</f>
-        <v>∡</v>
+        <v>∢</v>
       </c>
       <c r="H470" s="1" t="s">
         <v>1349</v>
@@ -22303,61 +22306,61 @@
     </row>
     <row r="471" spans="1:9" ht="16.95" customHeight="1">
       <c r="A471" s="1" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="B471" s="5">
         <f>IF(ISNA(VLOOKUP(H471,$A$2:$C$1028,3,1)),C471,VLOOKUP(H471,$A$2:$C$1028,3,1))</f>
-        <v>649</v>
+        <v>606</v>
       </c>
       <c r="C471" s="1">
-        <v>651</v>
+        <v>607</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="F471" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A471,3,4)))</f>
-        <v>∢</v>
+        <v>∣</v>
       </c>
       <c r="G471" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A471,3,4)))</f>
-        <v>∢</v>
+        <v>∣</v>
       </c>
       <c r="H471" s="1" t="s">
-        <v>1349</v>
+        <v>293</v>
       </c>
       <c r="I471" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H471,3,4)))</f>
-        <v>∠</v>
+        <v>|</v>
       </c>
     </row>
     <row r="472" spans="1:9" ht="16.95" customHeight="1">
       <c r="A472" s="1" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="B472" s="5">
         <f>IF(ISNA(VLOOKUP(H472,$A$2:$C$1028,3,1)),C472,VLOOKUP(H472,$A$2:$C$1028,3,1))</f>
         <v>606</v>
       </c>
       <c r="C472" s="1">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="F472" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A472,3,4)))</f>
-        <v>∣</v>
+        <v>∤</v>
       </c>
       <c r="G472" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A472,3,4)))</f>
-        <v>∣</v>
+        <v>∤</v>
       </c>
       <c r="H472" s="1" t="s">
         <v>293</v>
@@ -22369,28 +22372,28 @@
     </row>
     <row r="473" spans="1:9" ht="16.95" customHeight="1">
       <c r="A473" s="1" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B473" s="5">
         <f>IF(ISNA(VLOOKUP(H473,$A$2:$C$1028,3,1)),C473,VLOOKUP(H473,$A$2:$C$1028,3,1))</f>
         <v>606</v>
       </c>
       <c r="C473" s="1">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="F473" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A473,3,4)))</f>
-        <v>∤</v>
+        <v>∥</v>
       </c>
       <c r="G473" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A473,3,4)))</f>
-        <v>∤</v>
+        <v>∥</v>
       </c>
       <c r="H473" s="1" t="s">
         <v>293</v>
@@ -22402,28 +22405,28 @@
     </row>
     <row r="474" spans="1:9" ht="16.95" customHeight="1">
       <c r="A474" s="1" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="B474" s="5">
         <f>IF(ISNA(VLOOKUP(H474,$A$2:$C$1028,3,1)),C474,VLOOKUP(H474,$A$2:$C$1028,3,1))</f>
         <v>606</v>
       </c>
       <c r="C474" s="1">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="F474" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A474,3,4)))</f>
-        <v>∥</v>
+        <v>∦</v>
       </c>
       <c r="G474" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A474,3,4)))</f>
-        <v>∥</v>
+        <v>∦</v>
       </c>
       <c r="H474" s="1" t="s">
         <v>293</v>
@@ -22435,61 +22438,61 @@
     </row>
     <row r="475" spans="1:9" ht="16.95" customHeight="1">
       <c r="A475" s="1" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="B475" s="5">
         <f>IF(ISNA(VLOOKUP(H475,$A$2:$C$1028,3,1)),C475,VLOOKUP(H475,$A$2:$C$1028,3,1))</f>
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="C475" s="1">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="F475" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A475,3,4)))</f>
-        <v>∦</v>
+        <v>∧</v>
       </c>
       <c r="G475" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A475,3,4)))</f>
-        <v>∦</v>
+        <v>∧</v>
       </c>
       <c r="H475" s="1" t="s">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="I475" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H475,3,4)))</f>
-        <v>|</v>
+        <v>¬</v>
       </c>
     </row>
     <row r="476" spans="1:9" ht="16.95" customHeight="1">
       <c r="A476" s="1" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B476" s="5">
         <f>IF(ISNA(VLOOKUP(H476,$A$2:$C$1028,3,1)),C476,VLOOKUP(H476,$A$2:$C$1028,3,1))</f>
         <v>599</v>
       </c>
       <c r="C476" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="F476" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A476,3,4)))</f>
-        <v>∧</v>
+        <v>∨</v>
       </c>
       <c r="G476" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A476,3,4)))</f>
-        <v>∧</v>
+        <v>∨</v>
       </c>
       <c r="H476" s="1" t="s">
         <v>326</v>
@@ -22501,61 +22504,61 @@
     </row>
     <row r="477" spans="1:9" ht="16.95" customHeight="1">
       <c r="A477" s="1" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="B477" s="5">
         <f>IF(ISNA(VLOOKUP(H477,$A$2:$C$1028,3,1)),C477,VLOOKUP(H477,$A$2:$C$1028,3,1))</f>
-        <v>599</v>
+        <v>675</v>
       </c>
       <c r="C477" s="1">
-        <v>601</v>
+        <v>686</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="F477" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A477,3,4)))</f>
-        <v>∨</v>
+        <v>∩</v>
       </c>
       <c r="G477" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A477,3,4)))</f>
-        <v>∨</v>
-      </c>
-      <c r="H477" s="1" t="s">
-        <v>326</v>
+        <v>∩</v>
+      </c>
+      <c r="H477" s="20" t="s">
+        <v>1286</v>
       </c>
       <c r="I477" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H477,3,4)))</f>
-        <v>¬</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="478" spans="1:9" ht="16.95" customHeight="1">
       <c r="A478" s="1" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="B478" s="5">
         <f>IF(ISNA(VLOOKUP(H478,$A$2:$C$1028,3,1)),C478,VLOOKUP(H478,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C478" s="1">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="F478" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A478,3,4)))</f>
-        <v>∩</v>
+        <v>∪</v>
       </c>
       <c r="G478" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A478,3,4)))</f>
-        <v>∩</v>
+        <v>∪</v>
       </c>
       <c r="H478" s="20" t="s">
         <v>1286</v>
@@ -22567,61 +22570,61 @@
     </row>
     <row r="479" spans="1:9" ht="16.95" customHeight="1">
       <c r="A479" s="1" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="B479" s="5">
         <f>IF(ISNA(VLOOKUP(H479,$A$2:$C$1028,3,1)),C479,VLOOKUP(H479,$A$2:$C$1028,3,1))</f>
-        <v>675</v>
+        <v>638</v>
       </c>
       <c r="C479" s="1">
-        <v>687</v>
+        <v>638</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="F479" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A479,3,4)))</f>
-        <v>∪</v>
+        <v>∫</v>
       </c>
       <c r="G479" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A479,3,4)))</f>
-        <v>∪</v>
-      </c>
-      <c r="H479" s="20" t="s">
-        <v>1286</v>
+        <v>∫</v>
+      </c>
+      <c r="H479" s="1" t="s">
+        <v>1382</v>
       </c>
       <c r="I479" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H479,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∫</v>
       </c>
     </row>
     <row r="480" spans="1:9" ht="16.95" customHeight="1">
       <c r="A480" s="1" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="B480" s="5">
         <f>IF(ISNA(VLOOKUP(H480,$A$2:$C$1028,3,1)),C480,VLOOKUP(H480,$A$2:$C$1028,3,1))</f>
         <v>638</v>
       </c>
       <c r="C480" s="1">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="F480" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A480,3,4)))</f>
-        <v>∫</v>
+        <v>∬</v>
       </c>
       <c r="G480" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A480,3,4)))</f>
-        <v>∫</v>
+        <v>∬</v>
       </c>
       <c r="H480" s="1" t="s">
         <v>1382</v>
@@ -22633,28 +22636,28 @@
     </row>
     <row r="481" spans="1:9" ht="16.95" customHeight="1">
       <c r="A481" s="1" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B481" s="5">
         <f>IF(ISNA(VLOOKUP(H481,$A$2:$C$1028,3,1)),C481,VLOOKUP(H481,$A$2:$C$1028,3,1))</f>
         <v>638</v>
       </c>
       <c r="C481" s="1">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="F481" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A481,3,4)))</f>
-        <v>∬</v>
+        <v>∭</v>
       </c>
       <c r="G481" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A481,3,4)))</f>
-        <v>∬</v>
+        <v>∭</v>
       </c>
       <c r="H481" s="1" t="s">
         <v>1382</v>
@@ -22666,28 +22669,28 @@
     </row>
     <row r="482" spans="1:9" ht="16.95" customHeight="1">
       <c r="A482" s="1" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="B482" s="5">
         <f>IF(ISNA(VLOOKUP(H482,$A$2:$C$1028,3,1)),C482,VLOOKUP(H482,$A$2:$C$1028,3,1))</f>
         <v>638</v>
       </c>
       <c r="C482" s="1">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="F482" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A482,3,4)))</f>
-        <v>∭</v>
+        <v>∮</v>
       </c>
       <c r="G482" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A482,3,4)))</f>
-        <v>∭</v>
+        <v>∮</v>
       </c>
       <c r="H482" s="1" t="s">
         <v>1382</v>
@@ -22699,28 +22702,28 @@
     </row>
     <row r="483" spans="1:9" ht="16.95" customHeight="1">
       <c r="A483" s="1" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="B483" s="5">
         <f>IF(ISNA(VLOOKUP(H483,$A$2:$C$1028,3,1)),C483,VLOOKUP(H483,$A$2:$C$1028,3,1))</f>
         <v>638</v>
       </c>
       <c r="C483" s="1">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="F483" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A483,3,4)))</f>
-        <v>∮</v>
+        <v>∯</v>
       </c>
       <c r="G483" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A483,3,4)))</f>
-        <v>∮</v>
+        <v>∯</v>
       </c>
       <c r="H483" s="1" t="s">
         <v>1382</v>
@@ -22732,28 +22735,28 @@
     </row>
     <row r="484" spans="1:9" ht="16.95" customHeight="1">
       <c r="A484" s="1" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="B484" s="5">
         <f>IF(ISNA(VLOOKUP(H484,$A$2:$C$1028,3,1)),C484,VLOOKUP(H484,$A$2:$C$1028,3,1))</f>
         <v>638</v>
       </c>
       <c r="C484" s="1">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="F484" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A484,3,4)))</f>
-        <v>∯</v>
+        <v>∰</v>
       </c>
       <c r="G484" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A484,3,4)))</f>
-        <v>∯</v>
+        <v>∰</v>
       </c>
       <c r="H484" s="1" t="s">
         <v>1382</v>
@@ -22765,94 +22768,94 @@
     </row>
     <row r="485" spans="1:9" ht="16.95" customHeight="1">
       <c r="A485" s="1" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="B485" s="5">
         <f>IF(ISNA(VLOOKUP(H485,$A$2:$C$1028,3,1)),C485,VLOOKUP(H485,$A$2:$C$1028,3,1))</f>
-        <v>638</v>
+        <v>551</v>
       </c>
       <c r="C485" s="1">
-        <v>643</v>
+        <v>552</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="F485" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A485,3,4)))</f>
-        <v>∰</v>
+        <v>∶</v>
       </c>
       <c r="G485" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A485,3,4)))</f>
-        <v>∰</v>
+        <v>∶</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>1382</v>
+        <v>98</v>
       </c>
       <c r="I485" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H485,3,4)))</f>
-        <v>∫</v>
+        <v>:</v>
       </c>
     </row>
     <row r="486" spans="1:9" ht="16.95" customHeight="1">
       <c r="A486" s="1" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="B486" s="5">
         <f>IF(ISNA(VLOOKUP(H486,$A$2:$C$1028,3,1)),C486,VLOOKUP(H486,$A$2:$C$1028,3,1))</f>
-        <v>551</v>
+        <v>611</v>
       </c>
       <c r="C486" s="1">
-        <v>552</v>
+        <v>618</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="F486" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A486,3,4)))</f>
-        <v>∶</v>
+        <v>≃</v>
       </c>
       <c r="G486" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A486,3,4)))</f>
-        <v>∶</v>
+        <v>≃</v>
       </c>
       <c r="H486" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I486" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H486,3,4)))</f>
-        <v>:</v>
+        <v>≪</v>
       </c>
     </row>
     <row r="487" spans="1:9" ht="16.95" customHeight="1">
       <c r="A487" s="1" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="B487" s="5">
         <f>IF(ISNA(VLOOKUP(H487,$A$2:$C$1028,3,1)),C487,VLOOKUP(H487,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C487" s="1">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="F487" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A487,3,4)))</f>
-        <v>≃</v>
+        <v>≈</v>
       </c>
       <c r="G487" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A487,3,4)))</f>
-        <v>≃</v>
+        <v>≈</v>
       </c>
       <c r="H487" s="1" t="s">
         <v>107</v>
@@ -22864,28 +22867,28 @@
     </row>
     <row r="488" spans="1:9" ht="16.95" customHeight="1">
       <c r="A488" s="1" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="B488" s="5">
         <f>IF(ISNA(VLOOKUP(H488,$A$2:$C$1028,3,1)),C488,VLOOKUP(H488,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C488" s="1">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="F488" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A488,3,4)))</f>
-        <v>≈</v>
+        <v>≔</v>
       </c>
       <c r="G488" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A488,3,4)))</f>
-        <v>≈</v>
+        <v>≔</v>
       </c>
       <c r="H488" s="1" t="s">
         <v>107</v>
@@ -22897,28 +22900,28 @@
     </row>
     <row r="489" spans="1:9" ht="16.95" customHeight="1">
       <c r="A489" s="1" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="B489" s="5">
         <f>IF(ISNA(VLOOKUP(H489,$A$2:$C$1028,3,1)),C489,VLOOKUP(H489,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C489" s="1">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="F489" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A489,3,4)))</f>
-        <v>≔</v>
+        <v>≘</v>
       </c>
       <c r="G489" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A489,3,4)))</f>
-        <v>≔</v>
+        <v>≘</v>
       </c>
       <c r="H489" s="1" t="s">
         <v>107</v>
@@ -22930,28 +22933,28 @@
     </row>
     <row r="490" spans="1:9" ht="16.95" customHeight="1">
       <c r="A490" s="1" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="B490" s="5">
         <f>IF(ISNA(VLOOKUP(H490,$A$2:$C$1028,3,1)),C490,VLOOKUP(H490,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C490" s="1">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="F490" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A490,3,4)))</f>
-        <v>≘</v>
+        <v>≙</v>
       </c>
       <c r="G490" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A490,3,4)))</f>
-        <v>≘</v>
+        <v>≙</v>
       </c>
       <c r="H490" s="1" t="s">
         <v>107</v>
@@ -22963,28 +22966,28 @@
     </row>
     <row r="491" spans="1:9" ht="16.95" customHeight="1">
       <c r="A491" s="1" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="B491" s="5">
         <f>IF(ISNA(VLOOKUP(H491,$A$2:$C$1028,3,1)),C491,VLOOKUP(H491,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C491" s="1">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="F491" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A491,3,4)))</f>
-        <v>≙</v>
+        <v>≠</v>
       </c>
       <c r="G491" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A491,3,4)))</f>
-        <v>≙</v>
+        <v>≠</v>
       </c>
       <c r="H491" s="1" t="s">
         <v>107</v>
@@ -22996,28 +22999,28 @@
     </row>
     <row r="492" spans="1:9" ht="16.95" customHeight="1">
       <c r="A492" s="1" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="B492" s="5">
         <f>IF(ISNA(VLOOKUP(H492,$A$2:$C$1028,3,1)),C492,VLOOKUP(H492,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C492" s="1">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="F492" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A492,3,4)))</f>
-        <v>≠</v>
+        <v>≡</v>
       </c>
       <c r="G492" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A492,3,4)))</f>
-        <v>≠</v>
+        <v>≡</v>
       </c>
       <c r="H492" s="1" t="s">
         <v>107</v>
@@ -23029,28 +23032,28 @@
     </row>
     <row r="493" spans="1:9" ht="16.95" customHeight="1">
       <c r="A493" s="1" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="B493" s="5">
         <f>IF(ISNA(VLOOKUP(H493,$A$2:$C$1028,3,1)),C493,VLOOKUP(H493,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C493" s="1">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="F493" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A493,3,4)))</f>
-        <v>≡</v>
+        <v>≤</v>
       </c>
       <c r="G493" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A493,3,4)))</f>
-        <v>≡</v>
+        <v>≤</v>
       </c>
       <c r="H493" s="1" t="s">
         <v>107</v>
@@ -23062,28 +23065,28 @@
     </row>
     <row r="494" spans="1:9" ht="16.95" customHeight="1">
       <c r="A494" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="B494" s="5">
         <f>IF(ISNA(VLOOKUP(H494,$A$2:$C$1028,3,1)),C494,VLOOKUP(H494,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C494" s="1">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="F494" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A494,3,4)))</f>
-        <v>≤</v>
+        <v>≥</v>
       </c>
       <c r="G494" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A494,3,4)))</f>
-        <v>≤</v>
+        <v>≥</v>
       </c>
       <c r="H494" s="1" t="s">
         <v>107</v>
@@ -23095,28 +23098,28 @@
     </row>
     <row r="495" spans="1:9" ht="16.95" customHeight="1">
       <c r="A495" s="1" t="s">
-        <v>1427</v>
+        <v>107</v>
       </c>
       <c r="B495" s="5">
         <f>IF(ISNA(VLOOKUP(H495,$A$2:$C$1028,3,1)),C495,VLOOKUP(H495,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C495" s="1">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="F495" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A495,3,4)))</f>
-        <v>≥</v>
+        <v>≪</v>
       </c>
       <c r="G495" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A495,3,4)))</f>
-        <v>≥</v>
+        <v>≪</v>
       </c>
       <c r="H495" s="1" t="s">
         <v>107</v>
@@ -23128,28 +23131,28 @@
     </row>
     <row r="496" spans="1:9" ht="16.95" customHeight="1">
       <c r="A496" s="1" t="s">
-        <v>107</v>
+        <v>1432</v>
       </c>
       <c r="B496" s="5">
         <f>IF(ISNA(VLOOKUP(H496,$A$2:$C$1028,3,1)),C496,VLOOKUP(H496,$A$2:$C$1028,3,1))</f>
         <v>611</v>
       </c>
       <c r="C496" s="1">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="F496" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A496,3,4)))</f>
-        <v>≪</v>
+        <v>≫</v>
       </c>
       <c r="G496" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A496,3,4)))</f>
-        <v>≪</v>
+        <v>≫</v>
       </c>
       <c r="H496" s="1" t="s">
         <v>107</v>
@@ -23161,61 +23164,61 @@
     </row>
     <row r="497" spans="1:9" ht="16.95" customHeight="1">
       <c r="A497" s="1" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="B497" s="5">
         <f>IF(ISNA(VLOOKUP(H497,$A$2:$C$1028,3,1)),C497,VLOOKUP(H497,$A$2:$C$1028,3,1))</f>
-        <v>611</v>
+        <v>675</v>
       </c>
       <c r="C497" s="1">
-        <v>625</v>
+        <v>688</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="F497" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A497,3,4)))</f>
-        <v>≫</v>
+        <v>⊂</v>
       </c>
       <c r="G497" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A497,3,4)))</f>
-        <v>≫</v>
-      </c>
-      <c r="H497" s="1" t="s">
-        <v>107</v>
+        <v>⊂</v>
+      </c>
+      <c r="H497" s="20" t="s">
+        <v>1286</v>
       </c>
       <c r="I497" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H497,3,4)))</f>
-        <v>≪</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="498" spans="1:9" ht="16.95" customHeight="1">
       <c r="A498" s="1" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="B498" s="5">
         <f>IF(ISNA(VLOOKUP(H498,$A$2:$C$1028,3,1)),C498,VLOOKUP(H498,$A$2:$C$1028,3,1))</f>
         <v>675</v>
       </c>
       <c r="C498" s="1">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="F498" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A498,3,4)))</f>
-        <v>⊂</v>
+        <v>⊄</v>
       </c>
       <c r="G498" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A498,3,4)))</f>
-        <v>⊂</v>
+        <v>⊄</v>
       </c>
       <c r="H498" s="20" t="s">
         <v>1286</v>
@@ -23227,193 +23230,193 @@
     </row>
     <row r="499" spans="1:9" ht="16.95" customHeight="1">
       <c r="A499" s="1" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="B499" s="5">
         <f>IF(ISNA(VLOOKUP(H499,$A$2:$C$1028,3,1)),C499,VLOOKUP(H499,$A$2:$C$1028,3,1))</f>
-        <v>675</v>
+        <v>646</v>
       </c>
       <c r="C499" s="1">
-        <v>689</v>
+        <v>646</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="F499" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A499,3,4)))</f>
-        <v>⊄</v>
+        <v>⊕</v>
       </c>
       <c r="G499" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A499,3,4)))</f>
-        <v>⊄</v>
-      </c>
-      <c r="H499" s="20" t="s">
-        <v>1286</v>
+        <v>⊕</v>
+      </c>
+      <c r="H499" s="1" t="s">
+        <v>1441</v>
       </c>
       <c r="I499" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H499,3,4)))</f>
-        <v>Ɐ</v>
+        <v>⊕</v>
       </c>
     </row>
     <row r="500" spans="1:9" ht="16.95" customHeight="1">
       <c r="A500" s="1" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="B500" s="5">
         <f>IF(ISNA(VLOOKUP(H500,$A$2:$C$1028,3,1)),C500,VLOOKUP(H500,$A$2:$C$1028,3,1))</f>
-        <v>646</v>
+        <v>418</v>
       </c>
       <c r="C500" s="1">
-        <v>646</v>
+        <v>420</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="F500" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A500,3,4)))</f>
-        <v>⊕</v>
+        <v>⊖</v>
       </c>
       <c r="G500" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A500,3,4)))</f>
-        <v>⊕</v>
+        <v>⊖</v>
       </c>
       <c r="H500" s="1" t="s">
-        <v>1441</v>
+        <v>838</v>
       </c>
       <c r="I500" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H500,3,4)))</f>
-        <v>⊕</v>
+        <v>Α</v>
       </c>
     </row>
     <row r="501" spans="1:9" ht="16.95" customHeight="1">
       <c r="A501" s="1" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="B501" s="5">
         <f>IF(ISNA(VLOOKUP(H501,$A$2:$C$1028,3,1)),C501,VLOOKUP(H501,$A$2:$C$1028,3,1))</f>
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C501" s="1">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="F501" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A501,3,4)))</f>
-        <v>⊖</v>
+        <v>⊗</v>
       </c>
       <c r="G501" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A501,3,4)))</f>
-        <v>⊖</v>
+        <v>⊗</v>
       </c>
       <c r="H501" s="1" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="I501" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H501,3,4)))</f>
-        <v>Α</v>
+        <v>Δ</v>
       </c>
     </row>
     <row r="502" spans="1:9" ht="16.95" customHeight="1">
       <c r="A502" s="1" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="B502" s="5">
         <f>IF(ISNA(VLOOKUP(H502,$A$2:$C$1028,3,1)),C502,VLOOKUP(H502,$A$2:$C$1028,3,1))</f>
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C502" s="1">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="F502" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A502,3,4)))</f>
-        <v>⊗</v>
+        <v>⊘</v>
       </c>
       <c r="G502" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A502,3,4)))</f>
-        <v>⊗</v>
+        <v>⊘</v>
       </c>
       <c r="H502" s="1" t="s">
-        <v>847</v>
+        <v>338</v>
       </c>
       <c r="I502" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H502,3,4)))</f>
-        <v>Δ</v>
+        <v>Μ</v>
       </c>
     </row>
     <row r="503" spans="1:9" ht="16.95" customHeight="1">
       <c r="A503" s="1" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="B503" s="5">
         <f>IF(ISNA(VLOOKUP(H503,$A$2:$C$1028,3,1)),C503,VLOOKUP(H503,$A$2:$C$1028,3,1))</f>
-        <v>451</v>
+        <v>644</v>
       </c>
       <c r="C503" s="1">
-        <v>454</v>
+        <v>644</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="F503" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A503,3,4)))</f>
-        <v>⊘</v>
+        <v>⊙</v>
       </c>
       <c r="G503" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A503,3,4)))</f>
-        <v>⊘</v>
+        <v>⊙</v>
       </c>
       <c r="H503" s="1" t="s">
-        <v>338</v>
+        <v>1453</v>
       </c>
       <c r="I503" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H503,3,4)))</f>
-        <v>Μ</v>
+        <v>⊙</v>
       </c>
     </row>
     <row r="504" spans="1:9" ht="16.95" customHeight="1">
       <c r="A504" s="1" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="B504" s="5">
         <f>IF(ISNA(VLOOKUP(H504,$A$2:$C$1028,3,1)),C504,VLOOKUP(H504,$A$2:$C$1028,3,1))</f>
         <v>644</v>
       </c>
       <c r="C504" s="1">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="F504" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A504,3,4)))</f>
-        <v>⊙</v>
+        <v>⊚</v>
       </c>
       <c r="G504" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A504,3,4)))</f>
-        <v>⊙</v>
+        <v>⊚</v>
       </c>
       <c r="H504" s="1" t="s">
         <v>1453</v>
@@ -23425,61 +23428,61 @@
     </row>
     <row r="505" spans="1:9" ht="16.95" customHeight="1">
       <c r="A505" s="1" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="B505" s="5">
         <f>IF(ISNA(VLOOKUP(H505,$A$2:$C$1028,3,1)),C505,VLOOKUP(H505,$A$2:$C$1028,3,1))</f>
-        <v>644</v>
+        <v>319</v>
       </c>
       <c r="C505" s="1">
-        <v>645</v>
+        <v>332</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="F505" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A505,3,4)))</f>
-        <v>⊚</v>
+        <v>⊢</v>
       </c>
       <c r="G505" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A505,3,4)))</f>
-        <v>⊚</v>
+        <v>⊢</v>
       </c>
       <c r="H505" s="1" t="s">
-        <v>1453</v>
+        <v>177</v>
       </c>
       <c r="I505" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H505,3,4)))</f>
-        <v>⊙</v>
+        <v>T</v>
       </c>
     </row>
     <row r="506" spans="1:9" ht="16.95" customHeight="1">
       <c r="A506" s="1" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="B506" s="5">
         <f>IF(ISNA(VLOOKUP(H506,$A$2:$C$1028,3,1)),C506,VLOOKUP(H506,$A$2:$C$1028,3,1))</f>
         <v>319</v>
       </c>
       <c r="C506" s="1">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="F506" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A506,3,4)))</f>
-        <v>⊢</v>
+        <v>⊤</v>
       </c>
       <c r="G506" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A506,3,4)))</f>
-        <v>⊢</v>
+        <v>⊤</v>
       </c>
       <c r="H506" s="1" t="s">
         <v>177</v>
@@ -23491,94 +23494,94 @@
     </row>
     <row r="507" spans="1:9" ht="16.95" customHeight="1">
       <c r="A507" s="1" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="B507" s="5">
         <f>IF(ISNA(VLOOKUP(H507,$A$2:$C$1028,3,1)),C507,VLOOKUP(H507,$A$2:$C$1028,3,1))</f>
-        <v>319</v>
+        <v>647</v>
       </c>
       <c r="C507" s="1">
-        <v>322</v>
+        <v>648</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="F507" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A507,3,4)))</f>
-        <v>⊤</v>
+        <v>⊥</v>
       </c>
       <c r="G507" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A507,3,4)))</f>
-        <v>⊤</v>
+        <v>⊥</v>
       </c>
       <c r="H507" s="1" t="s">
-        <v>177</v>
+        <v>1346</v>
       </c>
       <c r="I507" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H507,3,4)))</f>
-        <v>T</v>
+        <v>∟</v>
       </c>
     </row>
     <row r="508" spans="1:9" ht="16.95" customHeight="1">
       <c r="A508" s="1" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="B508" s="5">
         <f>IF(ISNA(VLOOKUP(H508,$A$2:$C$1028,3,1)),C508,VLOOKUP(H508,$A$2:$C$1028,3,1))</f>
-        <v>647</v>
+        <v>599</v>
       </c>
       <c r="C508" s="1">
-        <v>648</v>
+        <v>602</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="F508" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A508,3,4)))</f>
-        <v>⊥</v>
+        <v>⊻</v>
       </c>
       <c r="G508" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A508,3,4)))</f>
-        <v>⊥</v>
+        <v>⊻</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>1346</v>
+        <v>326</v>
       </c>
       <c r="I508" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H508,3,4)))</f>
-        <v>∟</v>
+        <v>¬</v>
       </c>
     </row>
     <row r="509" spans="1:9" ht="16.95" customHeight="1">
       <c r="A509" s="1" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="B509" s="5">
         <f>IF(ISNA(VLOOKUP(H509,$A$2:$C$1028,3,1)),C509,VLOOKUP(H509,$A$2:$C$1028,3,1))</f>
         <v>599</v>
       </c>
       <c r="C509" s="1">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="F509" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A509,3,4)))</f>
-        <v>⊻</v>
+        <v>⊼</v>
       </c>
       <c r="G509" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A509,3,4)))</f>
-        <v>⊻</v>
+        <v>⊼</v>
       </c>
       <c r="H509" s="1" t="s">
         <v>326</v>
@@ -23590,28 +23593,28 @@
     </row>
     <row r="510" spans="1:9" ht="16.95" customHeight="1">
       <c r="A510" s="1" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="B510" s="5">
         <f>IF(ISNA(VLOOKUP(H510,$A$2:$C$1028,3,1)),C510,VLOOKUP(H510,$A$2:$C$1028,3,1))</f>
         <v>599</v>
       </c>
       <c r="C510" s="1">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="F510" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A510,3,4)))</f>
-        <v>⊼</v>
+        <v>⊽</v>
       </c>
       <c r="G510" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A510,3,4)))</f>
-        <v>⊼</v>
+        <v>⊽</v>
       </c>
       <c r="H510" s="1" t="s">
         <v>326</v>
@@ -23623,94 +23626,94 @@
     </row>
     <row r="511" spans="1:9" ht="16.95" customHeight="1">
       <c r="A511" s="1" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="B511" s="5">
         <f>IF(ISNA(VLOOKUP(H511,$A$2:$C$1028,3,1)),C511,VLOOKUP(H511,$A$2:$C$1028,3,1))</f>
-        <v>599</v>
+        <v>541</v>
       </c>
       <c r="C511" s="1">
-        <v>604</v>
+        <v>545</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="F511" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A511,3,4)))</f>
-        <v>⊽</v>
+        <v>⋅</v>
       </c>
       <c r="G511" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A511,3,4)))</f>
-        <v>⊽</v>
+        <v>⋅</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>326</v>
+        <v>59</v>
       </c>
       <c r="I511" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H511,3,4)))</f>
-        <v>¬</v>
+        <v>.</v>
       </c>
     </row>
     <row r="512" spans="1:9" ht="16.95" customHeight="1">
       <c r="A512" s="1" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="B512" s="5">
         <f>IF(ISNA(VLOOKUP(H512,$A$2:$C$1028,3,1)),C512,VLOOKUP(H512,$A$2:$C$1028,3,1))</f>
-        <v>541</v>
+        <v>652</v>
       </c>
       <c r="C512" s="1">
-        <v>545</v>
+        <v>655</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="F512" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A512,3,4)))</f>
-        <v>⋅</v>
+        <v>⌚</v>
       </c>
       <c r="G512" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A512,3,4)))</f>
-        <v>⋅</v>
-      </c>
-      <c r="H512" s="1" t="s">
-        <v>59</v>
+        <v>⌚</v>
+      </c>
+      <c r="H512" s="17" t="s">
+        <v>1483</v>
       </c>
       <c r="I512" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H512,3,4)))</f>
-        <v>.</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="513" spans="1:9" ht="16.95" customHeight="1">
       <c r="A513" s="1" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="B513" s="5">
         <f>IF(ISNA(VLOOKUP(H513,$A$2:$C$1028,3,1)),C513,VLOOKUP(H513,$A$2:$C$1028,3,1))</f>
         <v>652</v>
       </c>
       <c r="C513" s="1">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="F513" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A513,3,4)))</f>
-        <v>⌚</v>
+        <v>⌛</v>
       </c>
       <c r="G513" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A513,3,4)))</f>
-        <v>⌚</v>
+        <v>⌛</v>
       </c>
       <c r="H513" s="17" t="s">
         <v>1483</v>
@@ -23722,160 +23725,160 @@
     </row>
     <row r="514" spans="1:9" ht="16.95" customHeight="1">
       <c r="A514" s="1" t="s">
-        <v>1484</v>
+        <v>2022</v>
       </c>
       <c r="B514" s="5">
         <f>IF(ISNA(VLOOKUP(H514,$A$2:$C$1028,3,1)),C514,VLOOKUP(H514,$A$2:$C$1028,3,1))</f>
-        <v>652</v>
+        <v>578</v>
       </c>
       <c r="C514" s="1">
-        <v>653</v>
+        <v>581</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1485</v>
+        <v>2023</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>1486</v>
+        <v>1263</v>
       </c>
       <c r="F514" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A514,3,4)))</f>
-        <v>⌛</v>
+        <v>⎌</v>
       </c>
       <c r="G514" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A514,3,4)))</f>
-        <v>⌛</v>
-      </c>
-      <c r="H514" s="17" t="s">
-        <v>1483</v>
+        <v>⎌</v>
+      </c>
+      <c r="H514" s="1" t="s">
+        <v>1228</v>
       </c>
       <c r="I514" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H514,3,4)))</f>
-        <v>⎙</v>
+        <v>←</v>
       </c>
     </row>
     <row r="515" spans="1:9" ht="16.95" customHeight="1">
       <c r="A515" s="1" t="s">
-        <v>2022</v>
+        <v>1487</v>
       </c>
       <c r="B515" s="5">
         <f>IF(ISNA(VLOOKUP(H515,$A$2:$C$1028,3,1)),C515,VLOOKUP(H515,$A$2:$C$1028,3,1))</f>
-        <v>578</v>
+        <v>521</v>
       </c>
       <c r="C515" s="1">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>2023</v>
+        <v>1488</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1263</v>
+        <v>1489</v>
       </c>
       <c r="F515" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A515,3,4)))</f>
-        <v>⎌</v>
+        <v>⎓</v>
       </c>
       <c r="G515" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A515,3,4)))</f>
-        <v>⎌</v>
+        <v>⎓</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>1228</v>
+        <v>55</v>
       </c>
       <c r="I515" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H515,3,4)))</f>
-        <v>←</v>
+        <v>-</v>
       </c>
     </row>
     <row r="516" spans="1:9" ht="16.95" customHeight="1">
       <c r="A516" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="B516" s="5">
         <f>IF(ISNA(VLOOKUP(H516,$A$2:$C$1028,3,1)),C516,VLOOKUP(H516,$A$2:$C$1028,3,1))</f>
-        <v>521</v>
+        <v>652</v>
       </c>
       <c r="C516" s="1">
-        <v>525</v>
+        <v>652</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="F516" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A516,3,4)))</f>
-        <v>⎓</v>
+        <v>⎙</v>
       </c>
       <c r="G516" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A516,3,4)))</f>
-        <v>⎓</v>
-      </c>
-      <c r="H516" s="1" t="s">
-        <v>55</v>
+        <v>⎙</v>
+      </c>
+      <c r="H516" s="17" t="s">
+        <v>1483</v>
       </c>
       <c r="I516" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H516,3,4)))</f>
-        <v>-</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="517" spans="1:9" ht="16.95" customHeight="1">
       <c r="A517" s="1" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
       <c r="B517" s="5">
         <f>IF(ISNA(VLOOKUP(H517,$A$2:$C$1028,3,1)),C517,VLOOKUP(H517,$A$2:$C$1028,3,1))</f>
-        <v>652</v>
+        <v>499</v>
       </c>
       <c r="C517" s="1">
-        <v>652</v>
+        <v>500</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="F517" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A517,3,4)))</f>
-        <v>⎙</v>
+        <v>⎡</v>
       </c>
       <c r="G517" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A517,3,4)))</f>
-        <v>⎙</v>
-      </c>
-      <c r="H517" s="17" t="s">
-        <v>1483</v>
+        <v>⎡</v>
+      </c>
+      <c r="H517" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="I517" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H517,3,4)))</f>
-        <v>⎙</v>
+        <v>[</v>
       </c>
     </row>
     <row r="518" spans="1:9" ht="16.95" customHeight="1">
       <c r="A518" s="1" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="B518" s="5">
         <f>IF(ISNA(VLOOKUP(H518,$A$2:$C$1028,3,1)),C518,VLOOKUP(H518,$A$2:$C$1028,3,1))</f>
         <v>499</v>
       </c>
       <c r="C518" s="1">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="F518" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A518,3,4)))</f>
-        <v>⎡</v>
+        <v>⎢</v>
       </c>
       <c r="G518" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A518,3,4)))</f>
-        <v>⎡</v>
+        <v>⎢</v>
       </c>
       <c r="H518" s="1" t="s">
         <v>198</v>
@@ -23887,28 +23890,28 @@
     </row>
     <row r="519" spans="1:9" ht="16.95" customHeight="1">
       <c r="A519" s="1" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="B519" s="5">
         <f>IF(ISNA(VLOOKUP(H519,$A$2:$C$1028,3,1)),C519,VLOOKUP(H519,$A$2:$C$1028,3,1))</f>
         <v>499</v>
       </c>
       <c r="C519" s="1">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="F519" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A519,3,4)))</f>
-        <v>⎢</v>
+        <v>⎣</v>
       </c>
       <c r="G519" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A519,3,4)))</f>
-        <v>⎢</v>
+        <v>⎣</v>
       </c>
       <c r="H519" s="1" t="s">
         <v>198</v>
@@ -23920,28 +23923,28 @@
     </row>
     <row r="520" spans="1:9" ht="16.95" customHeight="1">
       <c r="A520" s="1" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="B520" s="5">
         <f>IF(ISNA(VLOOKUP(H520,$A$2:$C$1028,3,1)),C520,VLOOKUP(H520,$A$2:$C$1028,3,1))</f>
         <v>499</v>
       </c>
       <c r="C520" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="F520" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A520,3,4)))</f>
-        <v>⎣</v>
+        <v>⎤</v>
       </c>
       <c r="G520" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A520,3,4)))</f>
-        <v>⎣</v>
+        <v>⎤</v>
       </c>
       <c r="H520" s="1" t="s">
         <v>198</v>
@@ -23953,28 +23956,28 @@
     </row>
     <row r="521" spans="1:9" ht="16.95" customHeight="1">
       <c r="A521" s="1" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="B521" s="5">
         <f>IF(ISNA(VLOOKUP(H521,$A$2:$C$1028,3,1)),C521,VLOOKUP(H521,$A$2:$C$1028,3,1))</f>
         <v>499</v>
       </c>
       <c r="C521" s="1">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="F521" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A521,3,4)))</f>
-        <v>⎤</v>
+        <v>⎥</v>
       </c>
       <c r="G521" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A521,3,4)))</f>
-        <v>⎤</v>
+        <v>⎥</v>
       </c>
       <c r="H521" s="1" t="s">
         <v>198</v>
@@ -23986,28 +23989,28 @@
     </row>
     <row r="522" spans="1:9" ht="16.95" customHeight="1">
       <c r="A522" s="1" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="B522" s="5">
         <f>IF(ISNA(VLOOKUP(H522,$A$2:$C$1028,3,1)),C522,VLOOKUP(H522,$A$2:$C$1028,3,1))</f>
         <v>499</v>
       </c>
       <c r="C522" s="1">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="F522" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A522,3,4)))</f>
-        <v>⎥</v>
+        <v>⎦</v>
       </c>
       <c r="G522" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A522,3,4)))</f>
-        <v>⎥</v>
+        <v>⎦</v>
       </c>
       <c r="H522" s="1" t="s">
         <v>198</v>
@@ -24019,127 +24022,127 @@
     </row>
     <row r="523" spans="1:9" ht="16.95" customHeight="1">
       <c r="A523" s="1" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="B523" s="5">
         <f>IF(ISNA(VLOOKUP(H523,$A$2:$C$1028,3,1)),C523,VLOOKUP(H523,$A$2:$C$1028,3,1))</f>
-        <v>499</v>
+        <v>1</v>
       </c>
       <c r="C523" s="1">
-        <v>506</v>
+        <v>10</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="F523" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A523,3,4)))</f>
-        <v>⎦</v>
+        <v>⎵</v>
       </c>
       <c r="G523" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A523,3,4)))</f>
-        <v>⎦</v>
+        <v>⎵</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
       <c r="I523" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H523,3,4)))</f>
-        <v>[</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="524" spans="1:9" ht="16.95" customHeight="1">
       <c r="A524" s="1" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="B524" s="5">
         <f>IF(ISNA(VLOOKUP(H524,$A$2:$C$1028,3,1)),C524,VLOOKUP(H524,$A$2:$C$1028,3,1))</f>
-        <v>1</v>
+        <v>571</v>
       </c>
       <c r="C524" s="1">
-        <v>10</v>
+        <v>572</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="F524" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A524,3,4)))</f>
-        <v>⎵</v>
+        <v>⏦</v>
       </c>
       <c r="G524" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A524,3,4)))</f>
-        <v>⎵</v>
+        <v>⏦</v>
       </c>
       <c r="H524" s="1" t="s">
-        <v>9</v>
+        <v>299</v>
       </c>
       <c r="I524" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H524,3,4)))</f>
-        <v xml:space="preserve"> </v>
+        <v>~</v>
       </c>
     </row>
     <row r="525" spans="1:9" ht="16.95" customHeight="1">
       <c r="A525" s="1" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="B525" s="5">
         <f>IF(ISNA(VLOOKUP(H525,$A$2:$C$1028,3,1)),C525,VLOOKUP(H525,$A$2:$C$1028,3,1))</f>
-        <v>571</v>
+        <v>652</v>
       </c>
       <c r="C525" s="1">
-        <v>572</v>
+        <v>656</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="F525" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A525,3,4)))</f>
-        <v>⏦</v>
+        <v>⏱</v>
       </c>
       <c r="G525" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A525,3,4)))</f>
-        <v>⏦</v>
-      </c>
-      <c r="H525" s="1" t="s">
-        <v>299</v>
+        <v>⏱</v>
+      </c>
+      <c r="H525" s="17" t="s">
+        <v>1483</v>
       </c>
       <c r="I525" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H525,3,4)))</f>
-        <v>~</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="526" spans="1:9" ht="16.95" customHeight="1">
       <c r="A526" s="1" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="B526" s="5">
         <f>IF(ISNA(VLOOKUP(H526,$A$2:$C$1028,3,1)),C526,VLOOKUP(H526,$A$2:$C$1028,3,1))</f>
         <v>652</v>
       </c>
       <c r="C526" s="1">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="F526" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A526,3,4)))</f>
-        <v>⏱</v>
+        <v>⏻</v>
       </c>
       <c r="G526" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A526,3,4)))</f>
-        <v>⏱</v>
+        <v>⏻</v>
       </c>
       <c r="H526" s="17" t="s">
         <v>1483</v>
@@ -24151,40 +24154,40 @@
     </row>
     <row r="527" spans="1:9" ht="16.95" customHeight="1">
       <c r="A527" s="1" t="s">
-        <v>1519</v>
+        <v>2074</v>
       </c>
       <c r="B527" s="5">
         <f>IF(ISNA(VLOOKUP(H527,$A$2:$C$1028,3,1)),C527,VLOOKUP(H527,$A$2:$C$1028,3,1))</f>
-        <v>652</v>
+        <v>690</v>
       </c>
       <c r="C527" s="1">
-        <v>663</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>1520</v>
+        <v>695</v>
+      </c>
+      <c r="D527" t="s">
+        <v>2075</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1521</v>
+        <v>2065</v>
       </c>
       <c r="F527" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A527,3,4)))</f>
-        <v>⏻</v>
+        <v>␄</v>
       </c>
       <c r="G527" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A527,3,4)))</f>
-        <v>⏻</v>
-      </c>
-      <c r="H527" s="17" t="s">
-        <v>1483</v>
+        <v>␄</v>
+      </c>
+      <c r="H527" s="21" t="s">
+        <v>1522</v>
       </c>
       <c r="I527" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H527,3,4)))</f>
-        <v>⎙</v>
+        <v>␡</v>
       </c>
     </row>
     <row r="528" spans="1:9" ht="16.95" customHeight="1">
       <c r="A528" s="1" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="B528" s="5">
         <f>IF(ISNA(VLOOKUP(H528,$A$2:$C$1028,3,1)),C528,VLOOKUP(H528,$A$2:$C$1028,3,1))</f>
@@ -24194,10 +24197,10 @@
         <v>697</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="F528" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A528,3,4)))</f>
@@ -24217,7 +24220,7 @@
     </row>
     <row r="529" spans="1:9" ht="16.95" customHeight="1">
       <c r="A529" s="1" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="B529" s="5">
         <f>IF(ISNA(VLOOKUP(H529,$A$2:$C$1028,3,1)),C529,VLOOKUP(H529,$A$2:$C$1028,3,1))</f>
@@ -24227,10 +24230,10 @@
         <v>698</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="F529" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A529,3,4)))</f>
@@ -24419,16 +24422,16 @@
       </c>
       <c r="B535" s="5">
         <f>IF(ISNA(VLOOKUP(H535,$A$2:$C$1028,3,1)),C535,VLOOKUP(H535,$A$2:$C$1028,3,1))</f>
-        <v>690</v>
+        <v>569</v>
       </c>
       <c r="C535" s="1">
-        <v>695</v>
+        <v>570</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1535</v>
+        <v>303</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>2066</v>
+        <v>1538</v>
       </c>
       <c r="F535" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A535,3,4)))</f>
@@ -24438,12 +24441,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A535,3,4)))</f>
         <v>␧</v>
       </c>
-      <c r="H535" s="21" t="s">
-        <v>1522</v>
+      <c r="H535" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="I535" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H535,3,4)))</f>
-        <v>␡</v>
+        <v>_</v>
       </c>
     </row>
     <row r="536" spans="1:9" ht="16.95" customHeight="1">
@@ -29005,7 +29008,7 @@
     </row>
     <row r="674" spans="1:9" ht="16.95" customHeight="1">
       <c r="A674" s="1" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="B674" s="5">
         <f>IF(ISNA(VLOOKUP(H674,$A$2:$C$1028,3,1)),C674,VLOOKUP(H674,$A$2:$C$1028,3,1))</f>
@@ -29015,10 +29018,10 @@
         <v>699</v>
       </c>
       <c r="D674" s="2" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F674" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A674,3,4)))</f>
@@ -29038,7 +29041,7 @@
     </row>
     <row r="675" spans="1:9" ht="16.95" customHeight="1">
       <c r="A675" s="1" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="B675" s="5">
         <f>IF(ISNA(VLOOKUP(H675,$A$2:$C$1028,3,1)),C675,VLOOKUP(H675,$A$2:$C$1028,3,1))</f>
@@ -29048,10 +29051,10 @@
         <v>696</v>
       </c>
       <c r="D675" s="2" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="F675" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A675,3,4)))</f>
